--- a/8_Data_Synthesis/Data_Extraction.xlsx
+++ b/8_Data_Synthesis/Data_Extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/8_Data_Synthesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256E94C3-041A-9946-A297-B1E30244E28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4704409F-B9D4-E04C-927C-102DFB175B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15580" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15540" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -14704,7 +14704,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>3</c:v>
@@ -19213,16 +19213,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>189844</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>154069</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4767090</xdr:rowOff>
+      <xdr:rowOff>3497091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>589327</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>601490</xdr:rowOff>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>553552</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>4536703</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19249,16 +19249,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>342242</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1058690</xdr:rowOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>521116</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4993901</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>528509</xdr:colOff>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>707383</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>2582690</xdr:rowOff>
+      <xdr:rowOff>1312689</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20383,11 +20383,11 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <f t="shared" ref="AS3:AS15" si="4">SUMIF(F:F,AP3,AM:AM)</f>
+        <f>SUMIF(F:F,AP3,AM:AM)</f>
         <v>2</v>
       </c>
       <c r="AT3">
-        <f t="shared" ref="AT3:AT15" si="5">SUMIF(F:F,AP3,AN:AN)</f>
+        <f t="shared" ref="AT3:AT15" si="4">SUMIF(F:F,AP3,AN:AN)</f>
         <v>4</v>
       </c>
       <c r="AY3" t="s">
@@ -20737,7 +20737,7 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" ref="AK4:AK67" si="6">IF(Y4="PS",1,0)</f>
+        <f t="shared" ref="AK4:AK67" si="5">IF(Y4="PS",1,0)</f>
         <v>0</v>
       </c>
       <c r="AL4">
@@ -20756,7 +20756,7 @@
         <v>2014</v>
       </c>
       <c r="AQ4">
-        <f t="shared" ref="AQ4:AQ15" si="7">SUMIF(F:F,AP4,AK:AK)</f>
+        <f>SUMIF(F:F,AP4,AK:AK)</f>
         <v>7</v>
       </c>
       <c r="AR4">
@@ -20764,11 +20764,11 @@
         <v>0</v>
       </c>
       <c r="AS4">
+        <f t="shared" ref="AS3:AS15" si="6">SUMIF(F:F,AP4,AM:AM)</f>
+        <v>2</v>
+      </c>
+      <c r="AT4">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AT4">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="AY4" t="s">
@@ -20981,7 +20981,7 @@
         <v>0</v>
       </c>
       <c r="GQ4">
-        <f t="shared" ref="GQ4:GQ15" si="8">SUM(GI4,GL4,GN4)</f>
+        <f t="shared" ref="GQ4:GQ15" si="7">SUM(GI4,GL4,GN4)</f>
         <v>0</v>
       </c>
       <c r="GU4" t="s">
@@ -21129,7 +21129,7 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL5">
@@ -21148,7 +21148,7 @@
         <v>2015</v>
       </c>
       <c r="AQ5">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AQ4:AQ15" si="8">SUMIF(F:F,AP5,AK:AK)</f>
         <v>8</v>
       </c>
       <c r="AR5">
@@ -21156,11 +21156,11 @@
         <v>0</v>
       </c>
       <c r="AS5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="AY5" t="s">
@@ -21356,7 +21356,7 @@
         <v>0</v>
       </c>
       <c r="GQ5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GU5" t="s">
@@ -21502,7 +21502,7 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL6">
@@ -21521,7 +21521,7 @@
         <v>2016</v>
       </c>
       <c r="AQ6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="AR6">
@@ -21529,11 +21529,11 @@
         <v>0</v>
       </c>
       <c r="AS6">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AT6">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AT6">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="AY6" t="s">
@@ -21740,7 +21740,7 @@
         <v>0</v>
       </c>
       <c r="GQ6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ6">
@@ -21879,7 +21879,7 @@
         <v>0.5</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL7">
@@ -21898,7 +21898,7 @@
         <v>2017</v>
       </c>
       <c r="AQ7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="AR7">
@@ -21906,11 +21906,11 @@
         <v>0</v>
       </c>
       <c r="AS7">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AT7">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AT7">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="AY7" t="s">
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="GQ7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ7">
@@ -22223,9 +22223,11 @@
       <c r="AG8" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="AH8" s="2"/>
+      <c r="AH8" s="2">
+        <v>0</v>
+      </c>
       <c r="AK8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL8">
@@ -22244,7 +22246,7 @@
         <v>2018</v>
       </c>
       <c r="AQ8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="AR8">
@@ -22252,11 +22254,11 @@
         <v>0</v>
       </c>
       <c r="AS8">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AT8">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="AT8">
-        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="AY8" t="s">
@@ -22443,7 +22445,7 @@
         <v>1</v>
       </c>
       <c r="GQ8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ8">
@@ -22585,7 +22587,7 @@
         <v>1373</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL9">
@@ -22604,7 +22606,7 @@
         <v>2019</v>
       </c>
       <c r="AQ9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="AR9">
@@ -22612,11 +22614,11 @@
         <v>0</v>
       </c>
       <c r="AS9">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AT9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AT9">
-        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="AY9" t="s">
@@ -22798,7 +22800,7 @@
         <v>1</v>
       </c>
       <c r="GQ9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ9">
@@ -22941,7 +22943,7 @@
         <v>0.5</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL10">
@@ -22960,7 +22962,7 @@
         <v>2020</v>
       </c>
       <c r="AQ10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="AR10">
@@ -22968,11 +22970,11 @@
         <v>0</v>
       </c>
       <c r="AS10">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AT10">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AT10">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="AY10" t="s">
@@ -23178,7 +23180,7 @@
         <v>1</v>
       </c>
       <c r="GQ10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ10">
@@ -23317,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL11">
@@ -23336,7 +23338,7 @@
         <v>2021</v>
       </c>
       <c r="AQ11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="AR11">
@@ -23344,11 +23346,11 @@
         <v>0</v>
       </c>
       <c r="AS11">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AT11">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AT11">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="AY11" t="s">
@@ -23520,7 +23522,7 @@
         <v>1</v>
       </c>
       <c r="GQ11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ11">
@@ -23659,7 +23661,7 @@
         <v>0.5</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL12">
@@ -23678,7 +23680,7 @@
         <v>2022</v>
       </c>
       <c r="AQ12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="AR12">
@@ -23686,11 +23688,11 @@
         <v>1</v>
       </c>
       <c r="AS12">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AT12">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AT12">
-        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="BH12" t="s">
@@ -23726,9 +23728,8 @@
       <c r="CN12">
         <v>2022</v>
       </c>
-      <c r="CO12" cm="1">
-        <f t="array" ref="CO12">SUMPRODUCT((Y$2:Y$1000="PS")*(F$2:F$1000=$CN12)*(AH$2:AH$1000=0))</f>
-        <v>6</v>
+      <c r="CO12">
+        <v>7</v>
       </c>
       <c r="CP12" cm="1">
         <f t="array" ref="CP12">SUMPRODUCT((Y$2:Y$1000="PS")*(F$2:F$1000=$CN12)*(AH$2:AH$1000=0.5))</f>
@@ -23832,7 +23833,7 @@
         <v>1</v>
       </c>
       <c r="GQ12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ12">
@@ -23969,7 +23970,7 @@
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL13">
@@ -23988,7 +23989,7 @@
         <v>2023</v>
       </c>
       <c r="AQ13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="AR13">
@@ -23996,11 +23997,11 @@
         <v>0</v>
       </c>
       <c r="AS13">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AT13">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AT13">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="BH13" t="s">
@@ -24145,7 +24146,7 @@
         <v>0</v>
       </c>
       <c r="GQ13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ13">
@@ -24288,7 +24289,7 @@
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL14">
@@ -24307,7 +24308,7 @@
         <v>2024</v>
       </c>
       <c r="AQ14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="AR14">
@@ -24315,11 +24316,11 @@
         <v>1</v>
       </c>
       <c r="AS14">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AT14">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AT14">
-        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="CN14">
@@ -24431,7 +24432,7 @@
         <v>0</v>
       </c>
       <c r="GQ14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ14">
@@ -24570,7 +24571,7 @@
         <v>0.5</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL15">
@@ -24589,7 +24590,7 @@
         <v>2025</v>
       </c>
       <c r="AQ15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AR15">
@@ -24597,11 +24598,11 @@
         <v>0</v>
       </c>
       <c r="AS15">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AT15">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AT15">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="CN15">
@@ -24713,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="GQ15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="GZ15">
@@ -24850,7 +24851,7 @@
         <v>0.5</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL16">
@@ -24885,7 +24886,7 @@
       </c>
       <c r="CO16">
         <f>SUM(CO3:CO15)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CP16">
         <f>SUM(CP3:CP15)</f>
@@ -24902,7 +24903,7 @@
       </c>
       <c r="EW16">
         <f>SUM(CO16:CQ16)</f>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="FQ16" t="s">
         <v>1282</v>
@@ -24994,7 +24995,7 @@
         <v>1</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL17">
@@ -25098,7 +25099,7 @@
         <v>0.5</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL18">
@@ -25204,7 +25205,7 @@
         <v>0.5</v>
       </c>
       <c r="AK19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL19">
@@ -25350,7 +25351,7 @@
         <v>0.5</v>
       </c>
       <c r="AK20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL20">
@@ -25507,7 +25508,7 @@
         <v>0.5</v>
       </c>
       <c r="AK21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL21">
@@ -25666,7 +25667,7 @@
         <v>0.5</v>
       </c>
       <c r="AK22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL22">
@@ -25825,7 +25826,7 @@
         <v>0.5</v>
       </c>
       <c r="AK23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL23">
@@ -25981,7 +25982,7 @@
         <v>0.5</v>
       </c>
       <c r="AK24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL24">
@@ -26135,7 +26136,7 @@
         <v>0.5</v>
       </c>
       <c r="AK25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL25">
@@ -26294,7 +26295,7 @@
         <v>0.5</v>
       </c>
       <c r="AK26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL26">
@@ -26454,7 +26455,7 @@
         <v>0.5</v>
       </c>
       <c r="AK27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL27">
@@ -26608,7 +26609,7 @@
         <v>0</v>
       </c>
       <c r="AK28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL28">
@@ -26766,7 +26767,7 @@
         <v>0.5</v>
       </c>
       <c r="AK29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL29">
@@ -26922,7 +26923,7 @@
         <v>0.5</v>
       </c>
       <c r="AK30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL30">
@@ -27084,7 +27085,7 @@
         <v>0.5</v>
       </c>
       <c r="AK31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL31">
@@ -27244,7 +27245,7 @@
         <v>1</v>
       </c>
       <c r="AK32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL32">
@@ -27384,9 +27385,11 @@
       <c r="AE33" s="2"/>
       <c r="AF33" s="2"/>
       <c r="AG33" s="2"/>
-      <c r="AH33" s="2"/>
+      <c r="AH33" s="2">
+        <v>0</v>
+      </c>
       <c r="AK33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL33">
@@ -27493,7 +27496,7 @@
         <v>0.5</v>
       </c>
       <c r="AK34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL34">
@@ -27561,7 +27564,7 @@
         <v>1</v>
       </c>
       <c r="AK35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL35">
@@ -27632,7 +27635,7 @@
         <v>0.5</v>
       </c>
       <c r="AK36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL36">
@@ -27813,7 +27816,7 @@
         <v>1</v>
       </c>
       <c r="AK37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL37">
@@ -28027,7 +28030,7 @@
         <v>0</v>
       </c>
       <c r="AK38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL38">
@@ -28241,7 +28244,7 @@
         <v>0</v>
       </c>
       <c r="AK39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL39">
@@ -28455,7 +28458,7 @@
         <v>1</v>
       </c>
       <c r="AK40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL40">
@@ -28669,7 +28672,7 @@
         <v>1</v>
       </c>
       <c r="AK41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL41">
@@ -28885,7 +28888,7 @@
         <v>1</v>
       </c>
       <c r="AK42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL42">
@@ -29085,7 +29088,7 @@
       <c r="AG43" s="16"/>
       <c r="AH43" s="16"/>
       <c r="AK43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL43">
@@ -29299,7 +29302,7 @@
         <v>1</v>
       </c>
       <c r="AK44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL44">
@@ -29513,7 +29516,7 @@
         <v>555</v>
       </c>
       <c r="AK45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL45">
@@ -29713,7 +29716,7 @@
       <c r="AG46" s="17"/>
       <c r="AH46" s="17"/>
       <c r="AK46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL46">
@@ -29913,7 +29916,7 @@
       <c r="AG47" s="17"/>
       <c r="AH47" s="17"/>
       <c r="AK47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL47">
@@ -30127,7 +30130,7 @@
         <v>0.5</v>
       </c>
       <c r="AK48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL48">
@@ -30334,7 +30337,7 @@
         <v>0.5</v>
       </c>
       <c r="AK49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL49">
@@ -30541,7 +30544,7 @@
         <v>0</v>
       </c>
       <c r="AK50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL50">
@@ -30611,7 +30614,7 @@
         <v>0</v>
       </c>
       <c r="AK51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL51">
@@ -30680,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="AK52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL52">
@@ -30748,7 +30751,7 @@
         <v>0</v>
       </c>
       <c r="AK53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL53">
@@ -30816,7 +30819,7 @@
         <v>1</v>
       </c>
       <c r="AK54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL54">
@@ -30877,7 +30880,7 @@
         <v>0.5</v>
       </c>
       <c r="AK55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL55">
@@ -30940,7 +30943,7 @@
         <v>0.5</v>
       </c>
       <c r="AK56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL56">
@@ -31004,7 +31007,7 @@
         <v>0</v>
       </c>
       <c r="AK57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL57">
@@ -31051,7 +31054,7 @@
       <c r="AG58" s="20"/>
       <c r="AH58" s="20"/>
       <c r="AK58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL58">
@@ -31114,7 +31117,7 @@
         <v>0</v>
       </c>
       <c r="AK59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL59">
@@ -31177,7 +31180,7 @@
         <v>0</v>
       </c>
       <c r="AK60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL60">
@@ -31240,7 +31243,7 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL61">
@@ -31303,7 +31306,7 @@
         <v>0</v>
       </c>
       <c r="AK62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL62">
@@ -31366,7 +31369,7 @@
         <v>1</v>
       </c>
       <c r="AK63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL63">
@@ -31429,7 +31432,7 @@
         <v>0.5</v>
       </c>
       <c r="AK64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL64">
@@ -31525,7 +31528,7 @@
       <c r="AI65" s="26"/>
       <c r="AJ65" s="25"/>
       <c r="AK65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL65">
@@ -31625,7 +31628,7 @@
       <c r="AI66" s="26"/>
       <c r="AJ66" s="25"/>
       <c r="AK66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL66">
@@ -31721,7 +31724,7 @@
       <c r="AI67" s="26"/>
       <c r="AJ67" s="25"/>
       <c r="AK67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AL67">
@@ -31801,7 +31804,9 @@
       <c r="AE68" s="26"/>
       <c r="AF68" s="26"/>
       <c r="AG68" s="26"/>
-      <c r="AH68" s="26"/>
+      <c r="AH68" s="26">
+        <v>0</v>
+      </c>
       <c r="AI68" s="26" t="s">
         <v>751</v>
       </c>
@@ -31987,7 +31992,9 @@
       <c r="AE70" s="26"/>
       <c r="AF70" s="26"/>
       <c r="AG70" s="26"/>
-      <c r="AH70" s="26"/>
+      <c r="AH70" s="26">
+        <v>0</v>
+      </c>
       <c r="AI70" s="26" t="s">
         <v>751</v>
       </c>
@@ -32978,7 +32985,9 @@
       <c r="AE79" s="26"/>
       <c r="AF79" s="26"/>
       <c r="AG79" s="26"/>
-      <c r="AH79" s="26"/>
+      <c r="AH79" s="26">
+        <v>0</v>
+      </c>
       <c r="AI79" s="26" t="s">
         <v>751</v>
       </c>

--- a/8_Data_Synthesis/Data_Extraction.xlsx
+++ b/8_Data_Synthesis/Data_Extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/8_Data_Synthesis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\research\2026-SLR-regression-testing-optimization\8_Data_Synthesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4704409F-B9D4-E04C-927C-102DFB175B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B974F0A6-88CA-4A10-A9AE-A0C53BEDF5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15540" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
+    <workbookView xWindow="-23148" yWindow="1344" windowWidth="23256" windowHeight="13896" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -4844,9 +4844,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Collegamento ipertestuale" xfId="2" builtinId="8"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Valore non valido" xfId="1" builtinId="27"/>
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4864,7 +4864,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7498,7 +7498,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9240,7 +9240,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9709,7 +9709,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11572,7 +11572,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13438,7 +13438,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14219,7 +14219,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14588,7 +14588,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14622,6 +14622,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Foglio1!$CN$3:$CN$15</c:f>
@@ -14740,6 +14798,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Foglio1!$CN$3:$CN$15</c:f>
@@ -14858,6 +14974,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Foglio1!$CN$3:$CN$15</c:f>
@@ -14961,8 +15135,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -19323,7 +19498,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -19640,15 +19815,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA3DE9A-9DC8-9B4C-920E-613E1AA78E62}">
   <dimension ref="A1:HM126"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="27" max="27" width="22.1640625" customWidth="1"/>
-    <col min="30" max="30" width="21.1640625" customWidth="1"/>
-    <col min="32" max="32" width="8.6640625" customWidth="1"/>
-    <col min="33" max="33" width="50.1640625" customWidth="1"/>
+    <col min="27" max="27" width="22.19921875" customWidth="1"/>
+    <col min="30" max="30" width="21.19921875" customWidth="1"/>
+    <col min="32" max="32" width="8.69921875" customWidth="1"/>
+    <col min="33" max="33" width="50.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:221" ht="32">
+    <row r="1" spans="1:221">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20764,7 +20939,7 @@
         <v>0</v>
       </c>
       <c r="AS4">
-        <f t="shared" ref="AS3:AS15" si="6">SUMIF(F:F,AP4,AM:AM)</f>
+        <f t="shared" ref="AS4:AS15" si="6">SUMIF(F:F,AP4,AM:AM)</f>
         <v>2</v>
       </c>
       <c r="AT4">
@@ -21148,7 +21323,7 @@
         <v>2015</v>
       </c>
       <c r="AQ5">
-        <f t="shared" ref="AQ4:AQ15" si="8">SUMIF(F:F,AP5,AK:AK)</f>
+        <f t="shared" ref="AQ5:AQ15" si="8">SUMIF(F:F,AP5,AK:AK)</f>
         <v>8</v>
       </c>
       <c r="AR5">
@@ -27519,7 +27694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:221" ht="144">
+    <row r="35" spans="1:221" ht="115.2">
       <c r="C35" t="s">
         <v>458</v>
       </c>
@@ -27769,7 +27944,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="37" spans="1:221" ht="112">
+    <row r="37" spans="1:221" ht="100.8">
       <c r="C37" t="s">
         <v>477</v>
       </c>
@@ -27985,7 +28160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:221" ht="128">
+    <row r="38" spans="1:221" ht="115.2">
       <c r="C38" t="s">
         <v>486</v>
       </c>
@@ -28199,7 +28374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:221" ht="128">
+    <row r="39" spans="1:221" ht="100.8">
       <c r="C39" t="s">
         <v>495</v>
       </c>
@@ -28413,7 +28588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:221" ht="160">
+    <row r="40" spans="1:221" ht="144">
       <c r="C40" t="s">
         <v>504</v>
       </c>
@@ -28627,7 +28802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:221" ht="144">
+    <row r="41" spans="1:221" ht="115.2">
       <c r="C41" t="s">
         <v>512</v>
       </c>
@@ -28841,7 +29016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:221" ht="112">
+    <row r="42" spans="1:221" ht="100.8">
       <c r="C42" t="s">
         <v>521</v>
       </c>
@@ -29057,7 +29232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:221" ht="80">
+    <row r="43" spans="1:221" ht="57.6">
       <c r="C43" t="s">
         <v>531</v>
       </c>
@@ -29257,7 +29432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:221" ht="112">
+    <row r="44" spans="1:221" ht="100.8">
       <c r="C44" t="s">
         <v>536</v>
       </c>
@@ -29471,7 +29646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:221" ht="192">
+    <row r="45" spans="1:221" ht="158.4">
       <c r="C45" t="s">
         <v>545</v>
       </c>
@@ -29685,7 +29860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:221" ht="80">
+    <row r="46" spans="1:221" ht="57.6">
       <c r="C46" t="s">
         <v>556</v>
       </c>
@@ -29885,7 +30060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:221" ht="80">
+    <row r="47" spans="1:221" ht="57.6">
       <c r="C47" t="s">
         <v>561</v>
       </c>
@@ -30085,7 +30260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:221" ht="144">
+    <row r="48" spans="1:221" ht="129.6">
       <c r="C48" t="s">
         <v>565</v>
       </c>
@@ -30292,7 +30467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:221" ht="144">
+    <row r="49" spans="3:221" ht="129.6">
       <c r="C49" t="s">
         <v>574</v>
       </c>
@@ -30499,7 +30674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:221" ht="96">
+    <row r="50" spans="3:221" ht="86.4">
       <c r="C50" t="s">
         <v>583</v>
       </c>
@@ -30569,7 +30744,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="51" spans="3:221" ht="96">
+    <row r="51" spans="3:221" ht="86.4">
       <c r="C51" t="s">
         <v>592</v>
       </c>
@@ -30636,7 +30811,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="52" spans="3:221" ht="112">
+    <row r="52" spans="3:221" ht="86.4">
       <c r="C52" t="s">
         <v>600</v>
       </c>
@@ -30706,7 +30881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="3:221" ht="112">
+    <row r="53" spans="3:221" ht="100.8">
       <c r="C53" t="s">
         <v>609</v>
       </c>
@@ -30774,7 +30949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="3:221" ht="144">
+    <row r="54" spans="3:221" ht="129.6">
       <c r="C54" t="s">
         <v>618</v>
       </c>
@@ -30835,7 +31010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:221" ht="128">
+    <row r="55" spans="3:221" ht="115.2">
       <c r="C55" t="s">
         <v>626</v>
       </c>
@@ -30896,7 +31071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:221" ht="160">
+    <row r="56" spans="3:221" ht="144">
       <c r="C56" t="s">
         <v>635</v>
       </c>
@@ -30959,7 +31134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:221" ht="112">
+    <row r="57" spans="3:221" ht="100.8">
       <c r="C57" t="s">
         <v>643</v>
       </c>
@@ -31070,7 +31245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:221" ht="96">
+    <row r="59" spans="3:221" ht="86.4">
       <c r="C59" t="s">
         <v>656</v>
       </c>
@@ -31133,7 +31308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:221" ht="80">
+    <row r="60" spans="3:221" ht="57.6">
       <c r="C60" t="s">
         <v>664</v>
       </c>
@@ -31196,7 +31371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="3:221" ht="80">
+    <row r="61" spans="3:221" ht="72">
       <c r="C61" t="s">
         <v>671</v>
       </c>
@@ -31259,7 +31434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="3:221" ht="128">
+    <row r="62" spans="3:221" ht="115.2">
       <c r="C62" t="s">
         <v>680</v>
       </c>
@@ -31322,7 +31497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="3:221" ht="112">
+    <row r="63" spans="3:221" ht="100.8">
       <c r="C63" t="s">
         <v>689</v>
       </c>
@@ -31385,7 +31560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="3:221" ht="144">
+    <row r="64" spans="3:221" ht="115.2">
       <c r="C64" s="2" t="s">
         <v>696</v>
       </c>
@@ -31448,7 +31623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:180" ht="187">
+    <row r="65" spans="1:180" ht="140.4">
       <c r="A65" s="24">
         <v>9260075</v>
       </c>
@@ -31544,7 +31719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:180" ht="204">
+    <row r="66" spans="1:180" ht="187.2">
       <c r="A66" s="24">
         <v>8914670</v>
       </c>
@@ -31644,7 +31819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:180" ht="221">
+    <row r="67" spans="1:180" ht="187.2">
       <c r="A67" s="24">
         <v>8305938</v>
       </c>
@@ -31740,7 +31915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:180" ht="153">
+    <row r="68" spans="1:180" ht="140.4">
       <c r="A68" s="24">
         <v>8453107</v>
       </c>
@@ -31828,7 +32003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:180" ht="187">
+    <row r="69" spans="1:180" ht="124.8">
       <c r="A69" s="24">
         <v>8754416</v>
       </c>
@@ -31930,7 +32105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:180" ht="170">
+    <row r="70" spans="1:180" ht="140.4">
       <c r="A70" s="24">
         <v>7582788</v>
       </c>
@@ -32019,7 +32194,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="71" spans="1:180" ht="153">
+    <row r="71" spans="1:180" ht="124.8">
       <c r="A71" s="24" t="s">
         <v>772</v>
       </c>
@@ -32136,7 +32311,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="72" spans="1:180" ht="119">
+    <row r="72" spans="1:180" ht="93.6">
       <c r="A72" s="24" t="s">
         <v>790</v>
       </c>
@@ -32237,7 +32412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:180" ht="204">
+    <row r="73" spans="1:180" ht="156">
       <c r="A73" s="24" t="s">
         <v>803</v>
       </c>
@@ -32350,7 +32525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:180" ht="187">
+    <row r="74" spans="1:180" ht="171.6">
       <c r="A74" s="24" t="s">
         <v>818</v>
       </c>
@@ -32461,7 +32636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:180" ht="85">
+    <row r="75" spans="1:180" ht="78">
       <c r="A75" s="24" t="s">
         <v>831</v>
       </c>
@@ -32576,7 +32751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:180" ht="204">
+    <row r="76" spans="1:180" ht="187.2">
       <c r="A76" s="24" t="s">
         <v>844</v>
       </c>
@@ -32689,7 +32864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:180" ht="187">
+    <row r="77" spans="1:180" ht="140.4">
       <c r="A77" s="24" t="s">
         <v>856</v>
       </c>
@@ -32802,7 +32977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:180" ht="153">
+    <row r="78" spans="1:180" ht="124.8">
       <c r="A78" s="24" t="s">
         <v>872</v>
       </c>
@@ -32915,7 +33090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:180" ht="255">
+    <row r="79" spans="1:180" ht="202.8">
       <c r="A79" s="24" t="s">
         <v>884</v>
       </c>
@@ -33020,7 +33195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:180" ht="187">
+    <row r="80" spans="1:180" ht="140.4">
       <c r="A80" s="24" t="s">
         <v>895</v>
       </c>
@@ -33133,7 +33308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:180" ht="187">
+    <row r="81" spans="1:180" ht="156">
       <c r="A81" s="24" t="s">
         <v>909</v>
       </c>
@@ -33246,7 +33421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:180" ht="170">
+    <row r="82" spans="1:180" ht="124.8">
       <c r="A82" s="24"/>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
@@ -33327,7 +33502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:180" ht="187">
+    <row r="83" spans="1:180" ht="140.4">
       <c r="A83" s="24"/>
       <c r="B83" s="25"/>
       <c r="C83" s="26" t="s">
@@ -33422,7 +33597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:180" ht="187">
+    <row r="84" spans="1:180" ht="171.6">
       <c r="A84" s="24"/>
       <c r="B84" s="25"/>
       <c r="C84" s="26" t="s">
@@ -33517,7 +33692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:180" ht="170">
+    <row r="85" spans="1:180" ht="124.8">
       <c r="A85" s="24"/>
       <c r="B85" s="25"/>
       <c r="C85" s="26" t="s">
@@ -33603,7 +33778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:180" ht="102">
+    <row r="86" spans="1:180" ht="78">
       <c r="A86" s="24"/>
       <c r="B86" s="25"/>
       <c r="C86" s="26" t="s">
@@ -33673,7 +33848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:180" ht="136">
+    <row r="87" spans="1:180" ht="124.8">
       <c r="A87" s="24"/>
       <c r="B87" s="25"/>
       <c r="C87" s="26" t="s">
@@ -33743,7 +33918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:180" ht="153">
+    <row r="88" spans="1:180" ht="109.2">
       <c r="A88" s="24"/>
       <c r="B88" s="25"/>
       <c r="C88" s="26" t="s">
@@ -33813,7 +33988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:180" ht="136">
+    <row r="89" spans="1:180" ht="109.2">
       <c r="A89" s="24"/>
       <c r="B89" s="25"/>
       <c r="C89" s="26" t="s">
@@ -33983,7 +34158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:180" ht="153">
+    <row r="91" spans="1:180" ht="124.8">
       <c r="A91" s="24"/>
       <c r="B91" s="25"/>
       <c r="C91" s="26" t="s">
@@ -34067,7 +34242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:180" ht="372">
+    <row r="92" spans="1:180" ht="327.60000000000002">
       <c r="A92" s="24"/>
       <c r="B92" s="25"/>
       <c r="C92" s="26" t="s">
@@ -34151,7 +34326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:180" ht="102">
+    <row r="93" spans="1:180" ht="78">
       <c r="A93" s="24"/>
       <c r="B93" s="25"/>
       <c r="C93" s="26" t="s">
@@ -34221,7 +34396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:180" ht="153">
+    <row r="94" spans="1:180" ht="140.4">
       <c r="A94" s="24"/>
       <c r="B94" s="25"/>
       <c r="C94" s="26" t="s">
@@ -34305,7 +34480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:180" ht="119">
+    <row r="95" spans="1:180" ht="109.2">
       <c r="A95" s="24"/>
       <c r="B95" s="25"/>
       <c r="C95" s="26" t="s">
@@ -37023,7 +37198,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B91C968-CFFD-1A41-862E-46C430B19788}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="32"/>

--- a/8_Data_Synthesis/Data_Extraction.xlsx
+++ b/8_Data_Synthesis/Data_Extraction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/8_Data_Synthesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E57F04A-86BF-7448-8349-2EA684DEAAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DD1BB6-CE90-5F47-B700-5B79BDA8DDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15540" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="45740" windowHeight="22960" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -4317,9 +4317,6 @@
     <t>Heuristic greedy meta-heuristic</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>numero test selezionati</t>
   </si>
   <si>
@@ -4388,6 +4385,9 @@
   </si>
   <si>
     <t>2022, selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> selection</t>
   </si>
 </sst>
 </file>
@@ -4717,12 +4717,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5872,7 +5872,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -11818,7 +11818,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -13682,7 +13682,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
@@ -19690,28 +19690,28 @@
         <v>1310</v>
       </c>
       <c r="BO1" s="31" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="BP1" t="s">
         <v>66</v>
       </c>
       <c r="BQ1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="BR1" t="s">
         <v>1358</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>1359</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>1360</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>1361</v>
       </c>
       <c r="BU1" t="s">
         <v>1281</v>
       </c>
       <c r="BV1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="BX1" t="s">
         <v>1342</v>
@@ -19720,40 +19720,40 @@
         <v>66</v>
       </c>
       <c r="BZ1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="CA1" t="s">
         <v>1358</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>1359</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>1360</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>1361</v>
       </c>
       <c r="CD1" t="s">
         <v>1281</v>
       </c>
       <c r="CE1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="CG1" t="s">
         <v>1342</v>
       </c>
       <c r="CH1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="CI1" t="s">
         <v>1363</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="CK1" t="s">
         <v>1364</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>1361</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>1362</v>
       </c>
       <c r="CN1" t="s">
         <v>1319</v>
@@ -19762,19 +19762,19 @@
         <v>1274</v>
       </c>
       <c r="CV1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="CW1" t="s">
         <v>1366</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>1367</v>
       </c>
       <c r="CX1" t="s">
         <v>1252</v>
       </c>
       <c r="CY1" s="35" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="CZ1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="FQ1" s="31" t="s">
         <v>1229</v>
@@ -20257,19 +20257,19 @@
         <v>2013</v>
       </c>
       <c r="AQ3">
-        <f>SUMIF(F:F,AP3,AK:AK)</f>
+        <f t="shared" ref="AQ3:AQ15" si="3">SUMIF(F:F,AP3,AK:AK)</f>
         <v>4</v>
       </c>
       <c r="AR3">
-        <f>SUMIF(F:F,AP3,AL:AL)</f>
+        <f t="shared" ref="AR3:AR15" si="4">SUMIF(F:F,AP3,AL:AL)</f>
         <v>0</v>
       </c>
       <c r="AS3">
-        <f>SUMIF(F:F,AP3,AM:AM)</f>
+        <f t="shared" ref="AS3:AS15" si="5">SUMIF(F:F,AP3,AM:AM)</f>
         <v>1</v>
       </c>
       <c r="AT3">
-        <f>SUMIF(F:F,AP3,AN:AN)</f>
+        <f t="shared" ref="AT3:AT15" si="6">SUMIF(F:F,AP3,AN:AN)</f>
         <v>3</v>
       </c>
       <c r="AY3" t="s">
@@ -20330,19 +20330,19 @@
         <v>1252</v>
       </c>
       <c r="BP3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="BQ3" t="s">
         <v>1363</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BR3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="BS3" t="s">
         <v>1364</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
         <v>1361</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>1365</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>1362</v>
       </c>
       <c r="BX3" t="s">
         <v>90</v>
@@ -20374,13 +20374,13 @@
       <c r="CS3" s="36"/>
       <c r="CT3" s="36"/>
       <c r="CV3" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="CW3">
         <v>18</v>
       </c>
       <c r="CY3" s="35" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="CZ3" s="34">
         <v>1</v>
@@ -20619,7 +20619,7 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" ref="AK4:AK67" si="3">IF(Y4="PS",1,0)</f>
+        <f t="shared" ref="AK4:AK67" si="7">IF(Y4="PS",1,0)</f>
         <v>0</v>
       </c>
       <c r="AL4">
@@ -20638,19 +20638,19 @@
         <v>2014</v>
       </c>
       <c r="AQ4">
-        <f>SUMIF(F:F,AP4,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AR4">
-        <f>SUMIF(F:F,AP4,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS4">
-        <f>SUMIF(F:F,AP4,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT4">
-        <f>SUMIF(F:F,AP4,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AY4" t="s">
@@ -20758,13 +20758,13 @@
       <c r="CS4" s="36"/>
       <c r="CT4" s="36"/>
       <c r="CV4" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="CW4">
         <v>13</v>
       </c>
       <c r="CY4" s="35" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="CZ4">
         <v>1</v>
@@ -20863,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="GQ4">
-        <f t="shared" ref="GQ4:GQ15" si="4">SUM(GI4,GL4,GN4)</f>
+        <f t="shared" ref="GQ4:GQ15" si="8">SUM(GI4,GL4,GN4)</f>
         <v>0</v>
       </c>
       <c r="GU4" t="s">
@@ -21011,7 +21011,7 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL5">
@@ -21030,19 +21030,19 @@
         <v>2015</v>
       </c>
       <c r="AQ5">
-        <f>SUMIF(F:F,AP5,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="AR5">
-        <f>SUMIF(F:F,AP5,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS5">
-        <f>SUMIF(F:F,AP5,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AT5">
-        <f>SUMIF(F:F,AP5,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="AY5" t="s">
@@ -21132,13 +21132,13 @@
       <c r="CS5" s="36"/>
       <c r="CT5" s="36"/>
       <c r="CV5" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="CW5">
         <v>8</v>
       </c>
       <c r="CY5" s="35" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="CZ5" s="34">
         <v>4</v>
@@ -21238,7 +21238,7 @@
         <v>0</v>
       </c>
       <c r="GQ5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GU5" t="s">
@@ -21384,7 +21384,7 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL6">
@@ -21403,19 +21403,19 @@
         <v>2016</v>
       </c>
       <c r="AQ6">
-        <f>SUMIF(F:F,AP6,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="AR6">
-        <f>SUMIF(F:F,AP6,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS6">
-        <f>SUMIF(F:F,AP6,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AT6">
-        <f>SUMIF(F:F,AP6,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="AY6" t="s">
@@ -21517,13 +21517,13 @@
       <c r="CS6" s="36"/>
       <c r="CT6" s="36"/>
       <c r="CV6" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="CW6">
         <v>47</v>
       </c>
       <c r="CY6" s="35" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="CZ6" s="34">
         <v>8</v>
@@ -21622,7 +21622,7 @@
         <v>0</v>
       </c>
       <c r="GQ6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ6">
@@ -21761,7 +21761,7 @@
         <v>0.5</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL7">
@@ -21780,19 +21780,19 @@
         <v>2017</v>
       </c>
       <c r="AQ7">
-        <f>SUMIF(F:F,AP7,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AR7">
-        <f>SUMIF(F:F,AP7,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS7">
-        <f>SUMIF(F:F,AP7,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT7">
-        <f>SUMIF(F:F,AP7,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AY7" t="s">
@@ -21976,7 +21976,7 @@
         <v>0</v>
       </c>
       <c r="GQ7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ7">
@@ -22103,13 +22103,13 @@
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
       <c r="AG8" s="2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="AH8" s="2">
         <v>0</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL8">
@@ -22128,19 +22128,19 @@
         <v>2018</v>
       </c>
       <c r="AQ8">
-        <f>SUMIF(F:F,AP8,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AR8">
-        <f>SUMIF(F:F,AP8,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS8">
-        <f>SUMIF(F:F,AP8,AM:AM)</f>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="AT8">
-        <f>SUMIF(F:F,AP8,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="AY8" t="s">
@@ -22327,7 +22327,7 @@
         <v>1</v>
       </c>
       <c r="GQ8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ8">
@@ -22465,11 +22465,11 @@
       <c r="AH9" s="2">
         <v>0.5</v>
       </c>
-      <c r="AI9" s="38" t="s">
+      <c r="AI9" s="37" t="s">
         <v>1337</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL9">
@@ -22488,19 +22488,19 @@
         <v>2019</v>
       </c>
       <c r="AQ9">
-        <f>SUMIF(F:F,AP9,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AR9">
-        <f>SUMIF(F:F,AP9,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS9">
-        <f>SUMIF(F:F,AP9,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AT9">
-        <f>SUMIF(F:F,AP9,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="AY9" t="s">
@@ -22682,7 +22682,7 @@
         <v>1</v>
       </c>
       <c r="GQ9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ9">
@@ -22825,7 +22825,7 @@
         <v>0.5</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL10">
@@ -22844,19 +22844,19 @@
         <v>2020</v>
       </c>
       <c r="AQ10">
-        <f>SUMIF(F:F,AP10,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AR10">
-        <f>SUMIF(F:F,AP10,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS10">
-        <f>SUMIF(F:F,AP10,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT10">
-        <f>SUMIF(F:F,AP10,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AY10" t="s">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="BI10" cm="1">
         <f t="array" ref="BI10">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("modification"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ10" cm="1">
         <f t="array" ref="BJ10">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("modification"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("metaheuristic"),UPPER($AB$2:$AB$996))))+(ISNUMBER(FIND(UPPER("meta-heuristic"),UPPER($AB$2:$AB$996))))))</f>
@@ -23062,7 +23062,7 @@
         <v>1</v>
       </c>
       <c r="GQ10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ10">
@@ -23201,7 +23201,7 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL11">
@@ -23220,19 +23220,19 @@
         <v>2021</v>
       </c>
       <c r="AQ11">
-        <f>SUMIF(F:F,AP11,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AR11">
-        <f>SUMIF(F:F,AP11,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS11">
-        <f>SUMIF(F:F,AP11,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT11">
-        <f>SUMIF(F:F,AP11,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AY11" t="s">
@@ -23404,7 +23404,7 @@
         <v>1</v>
       </c>
       <c r="GQ11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ11">
@@ -23516,7 +23516,7 @@
         <v>58</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="AA12" s="2" t="s">
         <v>1330</v>
@@ -23543,7 +23543,7 @@
         <v>0.5</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL12">
@@ -23562,19 +23562,19 @@
         <v>2022</v>
       </c>
       <c r="AQ12">
-        <f>SUMIF(F:F,AP12,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="AR12">
-        <f>SUMIF(F:F,AP12,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS12">
-        <f>SUMIF(F:F,AP12,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT12">
-        <f>SUMIF(F:F,AP12,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="BH12" t="s">
@@ -23715,7 +23715,7 @@
         <v>1</v>
       </c>
       <c r="GQ12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ12">
@@ -23852,7 +23852,7 @@
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL13">
@@ -23871,19 +23871,19 @@
         <v>2023</v>
       </c>
       <c r="AQ13">
-        <f>SUMIF(F:F,AP13,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="AR13">
-        <f>SUMIF(F:F,AP13,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS13">
-        <f>SUMIF(F:F,AP13,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AT13">
-        <f>SUMIF(F:F,AP13,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="BH13" t="s">
@@ -24028,7 +24028,7 @@
         <v>0</v>
       </c>
       <c r="GQ13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ13">
@@ -24171,7 +24171,7 @@
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL14">
@@ -24190,19 +24190,19 @@
         <v>2024</v>
       </c>
       <c r="AQ14">
-        <f>SUMIF(F:F,AP14,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AR14">
-        <f>SUMIF(F:F,AP14,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AS14">
-        <f>SUMIF(F:F,AP14,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT14">
-        <f>SUMIF(F:F,AP14,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="CN14">
@@ -24314,7 +24314,7 @@
         <v>0</v>
       </c>
       <c r="GQ14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ14">
@@ -24453,7 +24453,7 @@
         <v>0.5</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL15">
@@ -24472,19 +24472,19 @@
         <v>2025</v>
       </c>
       <c r="AQ15">
-        <f>SUMIF(F:F,AP15,AK:AK)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AR15">
-        <f>SUMIF(F:F,AP15,AL:AL)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS15">
-        <f>SUMIF(F:F,AP15,AM:AM)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AT15">
-        <f>SUMIF(F:F,AP15,AN:AN)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="CN15">
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="GQ15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="GZ15">
@@ -24733,7 +24733,7 @@
         <v>0.5</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL16">
@@ -24877,7 +24877,7 @@
         <v>1</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL17">
@@ -24981,7 +24981,7 @@
         <v>0.5</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL18">
@@ -25087,7 +25087,7 @@
         <v>0.5</v>
       </c>
       <c r="AK19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL19">
@@ -25233,7 +25233,7 @@
         <v>0.5</v>
       </c>
       <c r="AK20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL20">
@@ -25390,7 +25390,7 @@
         <v>0.5</v>
       </c>
       <c r="AK21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL21">
@@ -25549,7 +25549,7 @@
         <v>0.5</v>
       </c>
       <c r="AK22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL22">
@@ -25708,7 +25708,7 @@
         <v>0.5</v>
       </c>
       <c r="AK23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL23">
@@ -25864,7 +25864,7 @@
         <v>0.5</v>
       </c>
       <c r="AK24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL24">
@@ -26018,7 +26018,7 @@
         <v>0.5</v>
       </c>
       <c r="AK25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL25">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="HC25" cm="1">
         <f t="array" ref="HC25">SUMPRODUCT((Y$2:Y$996="PS")*(F$2:F$996=GZ25)*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*ISNUMBER(SEARCH(LOWER("heuristic"),LOWER(AB$2:AB$996))))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="HD25" cm="1">
         <f t="array" ref="HD25">SUMPRODUCT((Y$2:Y$996="PS")*(F$2:F$996=GZ25)*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*ISNUMBER(SEARCH(LOWER("ml"),LOWER(AB$2:AB$996))))</f>
@@ -26177,7 +26177,7 @@
         <v>0.5</v>
       </c>
       <c r="AK26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL26">
@@ -26337,7 +26337,7 @@
         <v>0.5</v>
       </c>
       <c r="AK27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL27">
@@ -26491,7 +26491,7 @@
         <v>0</v>
       </c>
       <c r="AK28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL28">
@@ -26649,7 +26649,7 @@
         <v>0.5</v>
       </c>
       <c r="AK29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL29">
@@ -26805,7 +26805,7 @@
         <v>0.5</v>
       </c>
       <c r="AK30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL30">
@@ -26967,7 +26967,7 @@
         <v>0.5</v>
       </c>
       <c r="AK31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL31">
@@ -27127,7 +27127,7 @@
         <v>1</v>
       </c>
       <c r="AK32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL32">
@@ -27271,7 +27271,7 @@
         <v>0</v>
       </c>
       <c r="AK33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL33">
@@ -27378,7 +27378,7 @@
         <v>0.5</v>
       </c>
       <c r="AK34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL34">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="FR34" s="34" cm="1">
         <f t="array" ref="FR34">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ34),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:221" ht="144">
@@ -27446,7 +27446,7 @@
         <v>1</v>
       </c>
       <c r="AK35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL35">
@@ -27517,7 +27517,7 @@
         <v>0.5</v>
       </c>
       <c r="AK36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL36">
@@ -27698,7 +27698,7 @@
         <v>1</v>
       </c>
       <c r="AK37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL37">
@@ -27912,7 +27912,7 @@
         <v>0</v>
       </c>
       <c r="AK38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL38">
@@ -28126,7 +28126,7 @@
         <v>0</v>
       </c>
       <c r="AK39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AL39">
@@ -28315,7 +28315,7 @@
         <v>58</v>
       </c>
       <c r="Z40" s="13" t="s">
-        <v>1354</v>
+        <v>1377</v>
       </c>
       <c r="AA40" s="14" t="s">
         <v>129</v>
@@ -28340,7 +28340,7 @@
         <v>1</v>
       </c>
       <c r="AK40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL40">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="AM40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40">
         <f t="shared" si="2"/>
@@ -28554,7 +28554,7 @@
         <v>1</v>
       </c>
       <c r="AK41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL41">
@@ -28770,7 +28770,7 @@
         <v>1</v>
       </c>
       <c r="AK42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL42">
@@ -28829,7 +28829,7 @@
       </c>
       <c r="GE42" cm="1">
         <f t="array" ref="GE42">SUMPRODUCT((Y$2:Y$996="PS")*(F$2:F$996=FV42)*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*ISNUMBER(SEARCH("mod",LOWER(AA$2:AA$996))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GF42" cm="1">
         <f t="array" ref="GF42">SUMPRODUCT((Y$2:Y$996="PS")*(F$2:F$996=FV42)*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*ISNUMBER(SEARCH("firewall",LOWER(AA$2:AA$996))))</f>
@@ -28970,7 +28970,7 @@
       <c r="AG43" s="16"/>
       <c r="AH43" s="16"/>
       <c r="AK43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AL43">
@@ -29184,7 +29184,7 @@
         <v>1</v>
       </c>
       <c r="AK44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL44">
@@ -29398,7 +29398,7 @@
         <v>554</v>
       </c>
       <c r="AK45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL45">
@@ -29598,7 +29598,7 @@
       <c r="AG46" s="17"/>
       <c r="AH46" s="17"/>
       <c r="AK46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AL46">
@@ -29798,7 +29798,7 @@
       <c r="AG47" s="17"/>
       <c r="AH47" s="17"/>
       <c r="AK47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AL47">
@@ -30012,7 +30012,7 @@
         <v>0.5</v>
       </c>
       <c r="AK48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL48">
@@ -30219,7 +30219,7 @@
         <v>0.5</v>
       </c>
       <c r="AK49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL49">
@@ -30426,7 +30426,7 @@
         <v>0</v>
       </c>
       <c r="AK50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL50">
@@ -30496,7 +30496,7 @@
         <v>0</v>
       </c>
       <c r="AK51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL51">
@@ -30538,7 +30538,7 @@
         <v>58</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="AA52" s="18" t="s">
         <v>407</v>
@@ -30565,7 +30565,7 @@
         <v>0</v>
       </c>
       <c r="AK52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL52">
@@ -30633,7 +30633,7 @@
         <v>0</v>
       </c>
       <c r="AK53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL53">
@@ -30701,7 +30701,7 @@
         <v>1</v>
       </c>
       <c r="AK54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL54">
@@ -30762,7 +30762,7 @@
         <v>0.5</v>
       </c>
       <c r="AK55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL55">
@@ -30825,7 +30825,7 @@
         <v>0.5</v>
       </c>
       <c r="AK56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL56">
@@ -30858,7 +30858,7 @@
         <v>644</v>
       </c>
       <c r="M57" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Y57" t="s">
         <v>58</v>
@@ -30889,7 +30889,7 @@
         <v>0</v>
       </c>
       <c r="AK57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL57">
@@ -30934,7 +30934,7 @@
       <c r="AG58" s="20"/>
       <c r="AH58" s="20"/>
       <c r="AK58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AL58">
@@ -30997,7 +30997,7 @@
         <v>0</v>
       </c>
       <c r="AK59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL59">
@@ -31060,7 +31060,7 @@
         <v>0</v>
       </c>
       <c r="AK60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL60">
@@ -31123,7 +31123,7 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL61">
@@ -31186,7 +31186,7 @@
         <v>0</v>
       </c>
       <c r="AK62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL62">
@@ -31249,7 +31249,7 @@
         <v>1</v>
       </c>
       <c r="AK63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL63">
@@ -31312,7 +31312,7 @@
         <v>0.5</v>
       </c>
       <c r="AK64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL64">
@@ -31408,7 +31408,7 @@
       <c r="AI65" s="26"/>
       <c r="AJ65" s="25"/>
       <c r="AK65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL65">
@@ -31508,7 +31508,7 @@
       <c r="AI66" s="26"/>
       <c r="AJ66" s="25"/>
       <c r="AK66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL66">
@@ -31577,7 +31577,7 @@
         <v>58</v>
       </c>
       <c r="Z67" s="26" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="AA67" s="26" t="s">
         <v>114</v>
@@ -31604,19 +31604,19 @@
       <c r="AI67" s="26"/>
       <c r="AJ67" s="25"/>
       <c r="AK67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AL67">
-        <f t="shared" ref="AL67:AL122" si="5">IF(AND(Y67="PS",ISNUMBER(SEARCH("minimization",Z67))),1,0)</f>
+        <f t="shared" ref="AL67:AL122" si="9">IF(AND(Y67="PS",ISNUMBER(SEARCH("minimization",Z67))),1,0)</f>
         <v>0</v>
       </c>
       <c r="AM67">
-        <f t="shared" ref="AM67:AM122" si="6">IF(AND(Y67="PS",ISNUMBER(SEARCH("selection",Z67))),1,0)</f>
+        <f t="shared" ref="AM67:AM122" si="10">IF(AND(Y67="PS",ISNUMBER(SEARCH("selection",Z67))),1,0)</f>
         <v>0</v>
       </c>
       <c r="AN67">
-        <f t="shared" ref="AN67:AN122" si="7">IF(AND(Y67="PS",ISNUMBER(SEARCH("prioritization",Z67))),1,0)</f>
+        <f t="shared" ref="AN67:AN122" si="11">IF(AND(Y67="PS",ISNUMBER(SEARCH("prioritization",Z67))),1,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -31690,19 +31690,19 @@
       <c r="AI68" s="26"/>
       <c r="AJ68" s="25"/>
       <c r="AK68">
-        <f t="shared" ref="AK68:AK122" si="8">IF(Y68="PS",1,0)</f>
+        <f t="shared" ref="AK68:AK122" si="12">IF(Y68="PS",1,0)</f>
         <v>1</v>
       </c>
       <c r="AL68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -31792,19 +31792,19 @@
       <c r="AI69" s="26"/>
       <c r="AJ69" s="25"/>
       <c r="AK69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -31876,19 +31876,19 @@
       <c r="AI70" s="26"/>
       <c r="AJ70" s="25"/>
       <c r="AK70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="FV70" t="s">
@@ -31987,19 +31987,19 @@
       <c r="AI71" s="26"/>
       <c r="AJ71" s="25"/>
       <c r="AK71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV71" t="s">
@@ -32073,32 +32073,32 @@
       <c r="Z72" s="26" t="s">
         <v>797</v>
       </c>
-      <c r="AA72" s="37" t="s">
+      <c r="AA72" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AB72" s="37"/>
-      <c r="AC72" s="37"/>
-      <c r="AD72" s="37"/>
-      <c r="AE72" s="37"/>
-      <c r="AF72" s="37"/>
-      <c r="AG72" s="37"/>
-      <c r="AH72" s="37"/>
+      <c r="AB72" s="39"/>
+      <c r="AC72" s="39"/>
+      <c r="AD72" s="39"/>
+      <c r="AE72" s="39"/>
+      <c r="AF72" s="39"/>
+      <c r="AG72" s="39"/>
+      <c r="AH72" s="39"/>
       <c r="AI72" s="26"/>
       <c r="AJ72" s="25"/>
       <c r="AK72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="FV72">
@@ -32199,19 +32199,19 @@
       <c r="AI73" s="26"/>
       <c r="AJ73" s="25"/>
       <c r="AK73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV73">
@@ -32310,19 +32310,19 @@
       <c r="AI74" s="26"/>
       <c r="AJ74" s="25"/>
       <c r="AK74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV74">
@@ -32425,19 +32425,19 @@
       <c r="AI75" s="26"/>
       <c r="AJ75" s="25"/>
       <c r="AK75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV75">
@@ -32538,19 +32538,19 @@
       <c r="AI76" s="26"/>
       <c r="AJ76" s="25"/>
       <c r="AK76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV76">
@@ -32651,19 +32651,19 @@
       <c r="AI77" s="26"/>
       <c r="AJ77" s="25"/>
       <c r="AK77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="FV77">
@@ -32764,19 +32764,19 @@
       <c r="AI78" s="26"/>
       <c r="AJ78" s="25"/>
       <c r="AK78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV78">
@@ -32853,7 +32853,7 @@
         <v>1023</v>
       </c>
       <c r="AA79" s="26" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="AB79" s="26"/>
       <c r="AC79" s="26"/>
@@ -32867,19 +32867,19 @@
       <c r="AI79" s="26"/>
       <c r="AJ79" s="25"/>
       <c r="AK79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV79">
@@ -32980,19 +32980,19 @@
       <c r="AI80" s="26"/>
       <c r="AJ80" s="25"/>
       <c r="AK80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="FV80">
@@ -33093,19 +33093,19 @@
       <c r="AI81" s="26"/>
       <c r="AJ81" s="25"/>
       <c r="AK81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV81">
@@ -33161,32 +33161,32 @@
       <c r="Z82" s="26" t="s">
         <v>921</v>
       </c>
-      <c r="AA82" s="37" t="s">
+      <c r="AA82" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AB82" s="37"/>
-      <c r="AC82" s="37"/>
-      <c r="AD82" s="37"/>
-      <c r="AE82" s="37"/>
-      <c r="AF82" s="37"/>
-      <c r="AG82" s="37"/>
-      <c r="AH82" s="37"/>
+      <c r="AB82" s="39"/>
+      <c r="AC82" s="39"/>
+      <c r="AD82" s="39"/>
+      <c r="AE82" s="39"/>
+      <c r="AF82" s="39"/>
+      <c r="AG82" s="39"/>
+      <c r="AH82" s="39"/>
       <c r="AI82" s="26"/>
       <c r="AJ82" s="25"/>
       <c r="AK82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="FV82">
@@ -33269,19 +33269,19 @@
       <c r="AI83" s="26"/>
       <c r="AJ83" s="25"/>
       <c r="AK83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV83">
@@ -33364,19 +33364,19 @@
       <c r="AI84" s="26"/>
       <c r="AJ84" s="25"/>
       <c r="AK84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="FV84">
@@ -33461,19 +33461,19 @@
       </c>
       <c r="AJ85" s="25"/>
       <c r="AK85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33518,32 +33518,32 @@
       <c r="Z86" s="26" t="s">
         <v>949</v>
       </c>
-      <c r="AA86" s="37" t="s">
+      <c r="AA86" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AB86" s="37"/>
-      <c r="AC86" s="37"/>
-      <c r="AD86" s="37"/>
-      <c r="AE86" s="37"/>
-      <c r="AF86" s="37"/>
-      <c r="AG86" s="37"/>
-      <c r="AH86" s="37"/>
+      <c r="AB86" s="39"/>
+      <c r="AC86" s="39"/>
+      <c r="AD86" s="39"/>
+      <c r="AE86" s="39"/>
+      <c r="AF86" s="39"/>
+      <c r="AG86" s="39"/>
+      <c r="AH86" s="39"/>
       <c r="AI86" s="26"/>
       <c r="AJ86" s="25"/>
       <c r="AK86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33588,32 +33588,32 @@
       <c r="Z87" s="26" t="s">
         <v>921</v>
       </c>
-      <c r="AA87" s="37" t="s">
+      <c r="AA87" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AB87" s="37"/>
-      <c r="AC87" s="37"/>
-      <c r="AD87" s="37"/>
-      <c r="AE87" s="37"/>
-      <c r="AF87" s="37"/>
-      <c r="AG87" s="37"/>
-      <c r="AH87" s="37"/>
+      <c r="AB87" s="39"/>
+      <c r="AC87" s="39"/>
+      <c r="AD87" s="39"/>
+      <c r="AE87" s="39"/>
+      <c r="AF87" s="39"/>
+      <c r="AG87" s="39"/>
+      <c r="AH87" s="39"/>
       <c r="AI87" s="26"/>
       <c r="AJ87" s="25"/>
       <c r="AK87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33685,19 +33685,19 @@
       <c r="AI88" s="26"/>
       <c r="AJ88" s="25"/>
       <c r="AK88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33740,7 +33740,7 @@
         <v>58</v>
       </c>
       <c r="Z89" s="26" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="AA89" s="26" t="s">
         <v>1332</v>
@@ -33769,19 +33769,19 @@
       <c r="AI89" s="26"/>
       <c r="AJ89" s="25"/>
       <c r="AK89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33853,19 +33853,19 @@
       <c r="AI90" s="26"/>
       <c r="AJ90" s="25"/>
       <c r="AK90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33910,32 +33910,32 @@
       <c r="Z91" s="26" t="s">
         <v>982</v>
       </c>
-      <c r="AA91" s="37" t="s">
+      <c r="AA91" s="39" t="s">
         <v>983</v>
       </c>
-      <c r="AB91" s="37"/>
-      <c r="AC91" s="37"/>
-      <c r="AD91" s="37"/>
-      <c r="AE91" s="37"/>
-      <c r="AF91" s="37"/>
-      <c r="AG91" s="37"/>
-      <c r="AH91" s="37"/>
+      <c r="AB91" s="39"/>
+      <c r="AC91" s="39"/>
+      <c r="AD91" s="39"/>
+      <c r="AE91" s="39"/>
+      <c r="AF91" s="39"/>
+      <c r="AG91" s="39"/>
+      <c r="AH91" s="39"/>
       <c r="AI91" s="26"/>
       <c r="AJ91" s="25"/>
       <c r="AK91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM91">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34007,19 +34007,19 @@
       <c r="AI92" s="26"/>
       <c r="AJ92" s="25"/>
       <c r="AK92">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34064,32 +34064,32 @@
       <c r="Z93" s="26" t="s">
         <v>997</v>
       </c>
-      <c r="AA93" s="37" t="s">
+      <c r="AA93" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AB93" s="37"/>
-      <c r="AC93" s="37"/>
-      <c r="AD93" s="37"/>
-      <c r="AE93" s="37"/>
-      <c r="AF93" s="37"/>
-      <c r="AG93" s="37"/>
-      <c r="AH93" s="37"/>
+      <c r="AB93" s="39"/>
+      <c r="AC93" s="39"/>
+      <c r="AD93" s="39"/>
+      <c r="AE93" s="39"/>
+      <c r="AF93" s="39"/>
+      <c r="AG93" s="39"/>
+      <c r="AH93" s="39"/>
       <c r="AI93" s="26"/>
       <c r="AJ93" s="25"/>
       <c r="AK93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM93">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34162,19 +34162,19 @@
       </c>
       <c r="AI94" s="2"/>
       <c r="AK94">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34221,29 +34221,29 @@
       <c r="Z95" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="AA95" s="39"/>
-      <c r="AB95" s="39"/>
-      <c r="AC95" s="39"/>
-      <c r="AD95" s="39"/>
-      <c r="AE95" s="39"/>
-      <c r="AF95" s="39"/>
-      <c r="AG95" s="39"/>
-      <c r="AH95" s="39"/>
+      <c r="AA95" s="38"/>
+      <c r="AB95" s="38"/>
+      <c r="AC95" s="38"/>
+      <c r="AD95" s="38"/>
+      <c r="AE95" s="38"/>
+      <c r="AF95" s="38"/>
+      <c r="AG95" s="38"/>
+      <c r="AH95" s="38"/>
       <c r="AI95" s="2"/>
       <c r="AK95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM95">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34314,19 +34314,19 @@
       </c>
       <c r="AI96" s="2"/>
       <c r="AK96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34399,19 +34399,19 @@
       </c>
       <c r="AI97" s="2"/>
       <c r="AK97">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM97">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34482,19 +34482,19 @@
       </c>
       <c r="AI98" s="2"/>
       <c r="AK98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL98">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM98">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN98">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34567,19 +34567,19 @@
         <v>1044</v>
       </c>
       <c r="AK99">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL99">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM99">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN99">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34652,19 +34652,19 @@
         <v>1053</v>
       </c>
       <c r="AK100">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL100">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM100">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN100">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34737,19 +34737,19 @@
         <v>1053</v>
       </c>
       <c r="AK101">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM101">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN101">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34820,19 +34820,19 @@
       </c>
       <c r="AI102" s="2"/>
       <c r="AK102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM102">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN102">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34903,19 +34903,19 @@
       </c>
       <c r="AI103" s="2"/>
       <c r="AK103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -34988,19 +34988,19 @@
         <v>1082</v>
       </c>
       <c r="AK104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35075,19 +35075,19 @@
         <v>1091</v>
       </c>
       <c r="AK105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35156,19 +35156,19 @@
       </c>
       <c r="AI106" s="2"/>
       <c r="AK106">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM106">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN106">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35239,19 +35239,19 @@
       </c>
       <c r="AI107" s="2"/>
       <c r="AK107">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM107">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN107">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35326,19 +35326,19 @@
         <v>1114</v>
       </c>
       <c r="AK108">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL108">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM108">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN108">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35407,19 +35407,19 @@
       </c>
       <c r="AI109" s="2"/>
       <c r="AK109">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM109">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN109">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35490,19 +35490,19 @@
       </c>
       <c r="AI110" s="2"/>
       <c r="AK110">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL110">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM110">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN110">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35575,19 +35575,19 @@
         <v>1139</v>
       </c>
       <c r="AK111">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN111">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35658,19 +35658,19 @@
         <v>1146</v>
       </c>
       <c r="AK112">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM112">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN112">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35743,19 +35743,19 @@
         <v>1155</v>
       </c>
       <c r="AK113">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM113">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN113">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35828,19 +35828,19 @@
         <v>1162</v>
       </c>
       <c r="AK114">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM114">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN114">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -35915,19 +35915,19 @@
         <v>1171</v>
       </c>
       <c r="AK115">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL115">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM115">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN115">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -36000,19 +36000,19 @@
         <v>1181</v>
       </c>
       <c r="AK116">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL116">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM116">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN116">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -36085,19 +36085,19 @@
         <v>1191</v>
       </c>
       <c r="AK117">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM117">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN117">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -36170,19 +36170,19 @@
         <v>1199</v>
       </c>
       <c r="AK118">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL118">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN118">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -36253,19 +36253,19 @@
       </c>
       <c r="AI119" s="2"/>
       <c r="AK119">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM119">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AN119">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36338,19 +36338,19 @@
       </c>
       <c r="AI120" s="2"/>
       <c r="AK120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL120">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM120">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN120">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -36421,19 +36421,19 @@
         <v>1215</v>
       </c>
       <c r="AK121">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL121">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM121">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN121">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -36506,19 +36506,19 @@
         <v>1222</v>
       </c>
       <c r="AK122">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL122">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM122">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN122">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>

--- a/8_Data_Synthesis/Data_Extraction.xlsx
+++ b/8_Data_Synthesis/Data_Extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/8_Data_Synthesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DD1BB6-CE90-5F47-B700-5B79BDA8DDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E87E4D-F4D3-E048-9185-1E889CD36AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="45740" windowHeight="22960" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15560" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="1378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="1360">
   <si>
     <t>ID</t>
   </si>
@@ -3049,9 +3049,6 @@
     <t>Statement coverage</t>
   </si>
   <si>
-    <t>The greedy algorithm is used as a secondary objective together with defect proneness</t>
-  </si>
-  <si>
     <t>D. Hao, L. Zhang and H. Mei</t>
   </si>
   <si>
@@ -3361,9 +3358,6 @@
     <t>NRPA, APFD</t>
   </si>
   <si>
-    <t>Github repo, no proper archival https://github.com/moji1/tp_rl</t>
-  </si>
-  <si>
     <t>M Mahdieh, SH Mirian-Hosseinabadi, K Etemadi, A Nosrati, S Jalali</t>
   </si>
   <si>
@@ -3390,9 +3384,6 @@
   </si>
   <si>
     <t>Defect, bug history</t>
-  </si>
-  <si>
-    <t>data and code available in two separate github repos</t>
   </si>
   <si>
     <t>M Mahdieh, SH Mirian-Hosseinabadi, M Mahdieh</t>
@@ -3488,9 +3479,6 @@
     <t>Fault detection ability, number of detected faults</t>
   </si>
   <si>
-    <t>only code available on zenodo (no data)</t>
-  </si>
-  <si>
     <t>M Olsthoorn, A Panichella</t>
   </si>
   <si>
@@ -3515,9 +3503,6 @@
     <t>Fault-detection capability</t>
   </si>
   <si>
-    <t>available on zenodo</t>
-  </si>
-  <si>
     <t>M Al-Refai, S Ghosh, W Cazzola</t>
   </si>
   <si>
@@ -3584,9 +3569,6 @@
     <t>APFD corrected; running time</t>
   </si>
   <si>
-    <t>available on figshare</t>
-  </si>
-  <si>
     <t>H Spieker, A Gotlieb, D Marijan, M Mossige</t>
   </si>
   <si>
@@ -3659,9 +3641,6 @@
     <t>Fault-detection capability; APFD</t>
   </si>
   <si>
-    <t>dataset available</t>
-  </si>
-  <si>
     <t>MA Rahman, MA Hasan, MS Siddik</t>
   </si>
   <si>
@@ -3678,9 +3657,6 @@
   </si>
   <si>
     <t>seeded faults</t>
-  </si>
-  <si>
-    <t>no code nor artifacts (dataset public)</t>
   </si>
   <si>
     <t>Zhichao Chen, Junjie Chen, Weijing Wang, Jianyi Zhou, Meng Wang, Xiang Chen, Shan Zhou, Jianmin Wang</t>
@@ -3709,9 +3685,6 @@
     <t>possibility of getting logs (not possible in defect 4j)</t>
   </si>
   <si>
-    <t xml:space="preserve">artifacts available on github </t>
-  </si>
-  <si>
     <t>SW Thomas, H Hemmati, AE Hassan, D Blostein</t>
   </si>
   <si>
@@ -3730,9 +3703,6 @@
     <t>availability of text data</t>
   </si>
   <si>
-    <t>artifacts not found</t>
-  </si>
-  <si>
     <t>MG Epitropakis, S Yoo, M Harman, EK Burke</t>
   </si>
   <si>
@@ -3757,9 +3727,6 @@
     <t>APFD_C</t>
   </si>
   <si>
-    <t>some results still avilable on custom link https://www.epitropakis.co.uk/issta2015/</t>
-  </si>
-  <si>
     <t>A Sharif, D Marijan, M Liaaen</t>
   </si>
   <si>
@@ -3787,9 +3754,6 @@
     <t>APDF and NAPFD</t>
   </si>
   <si>
-    <t>originally available on github, now 404</t>
-  </si>
-  <si>
     <t>X Wang, S Zhang</t>
   </si>
   <si>
@@ -3817,9 +3781,6 @@
     <t>APFD; APFD_C</t>
   </si>
   <si>
-    <t>available upon request</t>
-  </si>
-  <si>
     <t>S Biswas, R Rathi, A Dutta, P Mitra, R Mall</t>
   </si>
   <si>
@@ -3839,9 +3800,6 @@
   </si>
   <si>
     <t>Different domains, ranging from 80 to 190k LOC, 15 to 1300 tests)</t>
-  </si>
-  <si>
-    <t>not very high quality work</t>
   </si>
   <si>
     <t>Aitor Arrieta, Joseba Andoni Agirre, Goiuria Sagardui</t>
@@ -3890,9 +3848,6 @@
     <t>30 Java program from github, different domains, locs from  3k to 80k</t>
   </si>
   <si>
-    <t>ponline appendix: https://www.cs.wm.edu/semeru/data/FSE16-TCPSTUDY/#tools</t>
-  </si>
-  <si>
     <t>Feng Li; Jianyi Zhou; Yinzhu Li; Dan Hao; Lu Zhang</t>
   </si>
   <si>
@@ -3911,9 +3866,6 @@
     <t>APFD, time effectiveness</t>
   </si>
   <si>
-    <t>figshare</t>
-  </si>
-  <si>
     <t>Anno</t>
   </si>
   <si>
@@ -4256,26 +4208,10 @@
     <t xml:space="preserve">Heuristic-based </t>
   </si>
   <si>
-    <r>
-      <t>ML-based / IR-based</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="-webkit-standard"/>
-      </rPr>
-      <t>: Utilizza tecniche di Machine Learning, Information Retrieval, o Natural Language Processing per prioritizzare/selezionare test case. Include approcci basati su topic modeling (LDA), recommender systems, TF-IDF, similarity measures su testo/codice, clustering, classification, etc.</t>
-    </r>
-  </si>
-  <si>
     <t>ML-based Transfer Learning-based</t>
   </si>
   <si>
     <t>Heuristic-based greedy</t>
-  </si>
-  <si>
-    <t>greed y</t>
   </si>
   <si>
     <t xml:space="preserve"> greedy</t>
@@ -4394,7 +4330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4493,11 +4429,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="-webkit-standard"/>
     </font>
     <font>
       <sz val="12"/>
@@ -4715,7 +4646,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
@@ -12978,7 +12909,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -19522,7 +19453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA3DE9A-9DC8-9B4C-920E-613E1AA78E62}">
   <dimension ref="A1:HM122"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="27" max="27" width="22.1640625" customWidth="1"/>
     <col min="30" max="30" width="21.1640625" customWidth="1"/>
@@ -19530,7 +19461,7 @@
     <col min="33" max="33" width="50.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:221" ht="32">
+    <row r="1" spans="1:221" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19634,162 +19565,162 @@
         <v>33</v>
       </c>
       <c r="AK1" s="30" t="s">
-        <v>1224</v>
+        <v>1208</v>
       </c>
       <c r="AL1" s="30" t="s">
-        <v>1225</v>
+        <v>1209</v>
       </c>
       <c r="AM1" s="30" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AN1" s="30" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AW1" s="31"/>
       <c r="AX1" s="31"/>
       <c r="AY1" s="31" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="AZ1" t="s">
         <v>91</v>
       </c>
       <c r="BA1" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="BB1" s="31" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="BC1" s="31" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
       <c r="BD1" s="31" t="s">
-        <v>1343</v>
+        <v>1325</v>
       </c>
       <c r="BE1" s="31" t="s">
-        <v>1310</v>
+        <v>1294</v>
       </c>
       <c r="BH1" s="31" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="BI1" s="31" t="s">
         <v>408</v>
       </c>
       <c r="BJ1" s="31" t="s">
-        <v>1348</v>
+        <v>1330</v>
       </c>
       <c r="BK1" s="31" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="BL1" s="31" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
       <c r="BM1" s="31" t="s">
         <v>206</v>
       </c>
       <c r="BN1" s="31" t="s">
-        <v>1310</v>
+        <v>1294</v>
       </c>
       <c r="BO1" s="31" t="s">
-        <v>1356</v>
+        <v>1338</v>
       </c>
       <c r="BP1" t="s">
         <v>66</v>
       </c>
       <c r="BQ1" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="BR1" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
       <c r="BS1" t="s">
-        <v>1359</v>
+        <v>1341</v>
       </c>
       <c r="BT1" t="s">
-        <v>1360</v>
+        <v>1342</v>
       </c>
       <c r="BU1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="BV1" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="BX1" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="BY1" t="s">
         <v>66</v>
       </c>
       <c r="BZ1" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="CA1" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
       <c r="CB1" t="s">
-        <v>1359</v>
+        <v>1341</v>
       </c>
       <c r="CC1" t="s">
-        <v>1360</v>
+        <v>1342</v>
       </c>
       <c r="CD1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="CE1" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="CG1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="CJ1" t="s">
         <v>1342</v>
       </c>
-      <c r="CH1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>1363</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>1360</v>
-      </c>
       <c r="CK1" t="s">
-        <v>1364</v>
+        <v>1346</v>
       </c>
       <c r="CL1" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="CN1" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="CU1" t="s">
-        <v>1274</v>
+        <v>1258</v>
       </c>
       <c r="CV1" t="s">
-        <v>1365</v>
+        <v>1347</v>
       </c>
       <c r="CW1" t="s">
-        <v>1366</v>
+        <v>1348</v>
       </c>
       <c r="CX1" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
       <c r="CY1" s="35" t="s">
-        <v>1365</v>
+        <v>1347</v>
       </c>
       <c r="CZ1" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="FQ1" s="31" t="s">
-        <v>1229</v>
+        <v>1213</v>
       </c>
       <c r="FR1" s="31"/>
       <c r="FS1" s="31"/>
       <c r="FT1" s="31"/>
       <c r="FV1" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="GZ1" t="s">
-        <v>1274</v>
+        <v>1258</v>
       </c>
     </row>
-    <row r="2" spans="1:221" ht="409.6">
+    <row r="2" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>10048797</v>
       </c>
@@ -19846,7 +19777,7 @@
       </c>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2" t="s">
@@ -19875,19 +19806,19 @@
         <v>0</v>
       </c>
       <c r="AP2" s="31" t="s">
-        <v>1223</v>
+        <v>1207</v>
       </c>
       <c r="AQ2" s="31" t="s">
-        <v>1226</v>
+        <v>1210</v>
       </c>
       <c r="AR2" s="31" t="s">
-        <v>1225</v>
+        <v>1209</v>
       </c>
       <c r="AS2" s="31" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AT2" s="31" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AY2" t="s">
         <v>407</v>
@@ -19917,7 +19848,7 @@
         <v>14</v>
       </c>
       <c r="BH2" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
       <c r="BI2" cm="1">
         <f t="array" ref="BI2">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("integer programming"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -19941,7 +19872,7 @@
       </c>
       <c r="BN2" cm="1">
         <f t="array" ref="BN2">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("integer programming"),UPPER($AA$2:$AA$996))))*(ISNUMBER(FIND(UPPER("greedy"),UPPER($AB$2:$AB$996)))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP2">
         <v>74</v>
@@ -19989,7 +19920,7 @@
         <v>4</v>
       </c>
       <c r="CG2" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
       <c r="CI2">
         <v>1</v>
@@ -20001,7 +19932,7 @@
         <v>2</v>
       </c>
       <c r="CN2" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -20025,34 +19956,34 @@
         <v>5</v>
       </c>
       <c r="FQ2" t="s">
-        <v>1230</v>
+        <v>1214</v>
       </c>
       <c r="FR2" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="FS2" t="s">
-        <v>1232</v>
+        <v>1216</v>
       </c>
       <c r="FT2" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="FV2" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="FW2" t="s">
         <v>407</v>
       </c>
       <c r="FX2" t="s">
-        <v>1282</v>
+        <v>1266</v>
       </c>
       <c r="FY2" t="s">
         <v>142</v>
       </c>
       <c r="FZ2" t="s">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="GA2" t="s">
-        <v>1284</v>
+        <v>1268</v>
       </c>
       <c r="GB2" t="s">
         <v>114</v>
@@ -20061,10 +19992,10 @@
         <v>60</v>
       </c>
       <c r="GD2" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
       <c r="GE2" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
       <c r="GF2" t="s">
         <v>291</v>
@@ -20085,34 +20016,34 @@
         <v>61</v>
       </c>
       <c r="GL2" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="GM2" t="s">
-        <v>1287</v>
+        <v>1271</v>
       </c>
       <c r="GN2" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
       <c r="GO2" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
       <c r="GP2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="GQ2" t="s">
-        <v>1315</v>
+        <v>1299</v>
       </c>
       <c r="GU2" t="s">
-        <v>1316</v>
+        <v>1300</v>
       </c>
       <c r="GV2" t="s">
-        <v>1317</v>
+        <v>1301</v>
       </c>
       <c r="GW2" t="s">
-        <v>1318</v>
+        <v>1302</v>
       </c>
       <c r="GZ2" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="HA2" t="s">
         <v>46</v>
@@ -20124,37 +20055,37 @@
         <v>91</v>
       </c>
       <c r="HD2" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
       <c r="HE2" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
       <c r="HF2" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
       <c r="HG2" t="s">
         <v>60</v>
       </c>
       <c r="HH2" t="s">
-        <v>1306</v>
+        <v>1290</v>
       </c>
       <c r="HI2" t="s">
-        <v>1307</v>
+        <v>1291</v>
       </c>
       <c r="HJ2" t="s">
-        <v>1308</v>
+        <v>1292</v>
       </c>
       <c r="HK2" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="HL2" t="s">
-        <v>1310</v>
+        <v>1294</v>
       </c>
       <c r="HM2" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
     </row>
-    <row r="3" spans="1:221" ht="409.6">
+    <row r="3" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>8377903</v>
       </c>
@@ -20217,7 +20148,7 @@
         <v>60</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>62</v>
@@ -20300,7 +20231,7 @@
         <v>0</v>
       </c>
       <c r="BH3" t="s">
-        <v>1345</v>
+        <v>1327</v>
       </c>
       <c r="BI3" cm="1">
         <f t="array" ref="BI3">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("data-flow"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -20327,22 +20258,22 @@
         <v>0</v>
       </c>
       <c r="BO3" s="32" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
       <c r="BP3" t="s">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="BQ3" t="s">
-        <v>1363</v>
+        <v>1345</v>
       </c>
       <c r="BR3" t="s">
-        <v>1360</v>
+        <v>1342</v>
       </c>
       <c r="BS3" t="s">
-        <v>1364</v>
+        <v>1346</v>
       </c>
       <c r="BT3" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="BX3" t="s">
         <v>90</v>
@@ -20354,7 +20285,7 @@
         <v>1</v>
       </c>
       <c r="CG3" t="s">
-        <v>1345</v>
+        <v>1327</v>
       </c>
       <c r="CN3">
         <v>2013</v>
@@ -20374,13 +20305,13 @@
       <c r="CS3" s="36"/>
       <c r="CT3" s="36"/>
       <c r="CV3" t="s">
-        <v>1367</v>
+        <v>1349</v>
       </c>
       <c r="CW3">
         <v>18</v>
       </c>
       <c r="CY3" s="35" t="s">
-        <v>1367</v>
+        <v>1349</v>
       </c>
       <c r="CZ3" s="34">
         <v>1</v>
@@ -20389,7 +20320,7 @@
       <c r="DH3" s="33"/>
       <c r="DI3" s="33"/>
       <c r="FQ3" t="s">
-        <v>1234</v>
+        <v>1218</v>
       </c>
       <c r="FR3" s="34" cm="1">
         <f t="array" ref="FR3">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ3),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -20547,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:221" ht="409.6">
+    <row r="4" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>10197719</v>
       </c>
@@ -20681,7 +20612,7 @@
         <v>0</v>
       </c>
       <c r="BH4" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
       <c r="BI4" cm="1">
         <f t="array" ref="BI4">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("symbolic"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -20738,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="CG4" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
       <c r="CN4">
         <v>2014</v>
@@ -20758,13 +20689,13 @@
       <c r="CS4" s="36"/>
       <c r="CT4" s="36"/>
       <c r="CV4" t="s">
-        <v>1368</v>
+        <v>1350</v>
       </c>
       <c r="CW4">
         <v>13</v>
       </c>
       <c r="CY4" s="35" t="s">
-        <v>1368</v>
+        <v>1350</v>
       </c>
       <c r="CZ4">
         <v>1</v>
@@ -20773,7 +20704,7 @@
       <c r="DI4" s="33"/>
       <c r="DS4" s="33"/>
       <c r="FQ4" t="s">
-        <v>1235</v>
+        <v>1219</v>
       </c>
       <c r="FR4" s="34" cm="1">
         <f t="array" ref="FR4">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ4),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -20931,7 +20862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:221" ht="409.6">
+    <row r="5" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>7515934</v>
       </c>
@@ -21046,7 +20977,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="s">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="AZ5" cm="1">
         <f t="array" ref="AZ5">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("prioritization"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("distribution"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -21073,7 +21004,7 @@
         <v>0</v>
       </c>
       <c r="BH5" t="s">
-        <v>1346</v>
+        <v>1328</v>
       </c>
       <c r="BI5" cm="1">
         <f t="array" ref="BI5">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("dynamic"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -21100,7 +21031,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="s">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="BY5">
         <v>6</v>
@@ -21112,7 +21043,7 @@
         <v>1</v>
       </c>
       <c r="CG5" t="s">
-        <v>1346</v>
+        <v>1328</v>
       </c>
       <c r="CN5">
         <v>2015</v>
@@ -21132,13 +21063,13 @@
       <c r="CS5" s="36"/>
       <c r="CT5" s="36"/>
       <c r="CV5" t="s">
-        <v>1369</v>
+        <v>1351</v>
       </c>
       <c r="CW5">
         <v>8</v>
       </c>
       <c r="CY5" s="35" t="s">
-        <v>1369</v>
+        <v>1351</v>
       </c>
       <c r="CZ5" s="34">
         <v>4</v>
@@ -21148,7 +21079,7 @@
       <c r="DI5" s="33"/>
       <c r="DT5" s="33"/>
       <c r="FQ5" t="s">
-        <v>1236</v>
+        <v>1220</v>
       </c>
       <c r="FR5" s="34" cm="1">
         <f t="array" ref="FR5">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ5),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -21306,7 +21237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:221" ht="409.6">
+    <row r="6" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6888744</v>
       </c>
@@ -21362,7 +21293,7 @@
         <v>104</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>1228</v>
+        <v>1212</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>91</v>
@@ -21419,7 +21350,7 @@
         <v>7</v>
       </c>
       <c r="AY6" t="s">
-        <v>1344</v>
+        <v>1326</v>
       </c>
       <c r="AZ6" cm="1">
         <f t="array" ref="AZ6">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("prioritization"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("human"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -21473,7 +21404,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="s">
-        <v>1344</v>
+        <v>1326</v>
       </c>
       <c r="BY6">
         <v>2</v>
@@ -21517,13 +21448,13 @@
       <c r="CS6" s="36"/>
       <c r="CT6" s="36"/>
       <c r="CV6" t="s">
-        <v>1370</v>
+        <v>1352</v>
       </c>
       <c r="CW6">
         <v>47</v>
       </c>
       <c r="CY6" s="35" t="s">
-        <v>1370</v>
+        <v>1352</v>
       </c>
       <c r="CZ6" s="34">
         <v>8</v>
@@ -21532,7 +21463,7 @@
       <c r="DH6" s="33"/>
       <c r="DI6" s="33"/>
       <c r="FQ6" t="s">
-        <v>1237</v>
+        <v>1221</v>
       </c>
       <c r="FR6" s="34" cm="1">
         <f t="array" ref="FR6">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ6),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -21681,7 +21612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:221" ht="409.6">
+    <row r="7" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>7809434</v>
       </c>
@@ -21740,7 +21671,7 @@
         <v>114</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>115</v>
@@ -21796,7 +21727,7 @@
         <v>6</v>
       </c>
       <c r="AY7" t="s">
-        <v>1284</v>
+        <v>1268</v>
       </c>
       <c r="AZ7" cm="1">
         <f t="array" ref="AZ7">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("prioritization"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("clustering"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -21823,7 +21754,7 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
       <c r="BI7" cm="1">
         <f t="array" ref="BI7">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("textual difference"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -21850,7 +21781,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="s">
-        <v>1284</v>
+        <v>1268</v>
       </c>
       <c r="BY7">
         <v>2</v>
@@ -21862,7 +21793,7 @@
         <v>1</v>
       </c>
       <c r="CG7" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
       <c r="CN7">
         <v>2017</v>
@@ -21886,7 +21817,7 @@
       <c r="DH7" s="33"/>
       <c r="DI7" s="33"/>
       <c r="FQ7" t="s">
-        <v>1238</v>
+        <v>1222</v>
       </c>
       <c r="FR7" s="34" cm="1">
         <f t="array" ref="FR7">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ7),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -22035,7 +21966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:221" ht="409.6">
+    <row r="8" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6571611</v>
       </c>
@@ -22103,7 +22034,7 @@
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
       <c r="AG8" s="2" t="s">
-        <v>1354</v>
+        <v>1336</v>
       </c>
       <c r="AH8" s="2">
         <v>0</v>
@@ -22171,7 +22102,7 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
       <c r="BI8" cm="1">
         <f t="array" ref="BI8">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("sdg"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -22213,7 +22144,7 @@
         <v>3</v>
       </c>
       <c r="CG8" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
       <c r="CN8">
         <v>2018</v>
@@ -22237,7 +22168,7 @@
       <c r="DH8" s="33"/>
       <c r="DI8" s="33"/>
       <c r="FQ8" t="s">
-        <v>1239</v>
+        <v>1223</v>
       </c>
       <c r="FR8" s="34" cm="1">
         <f t="array" ref="FR8">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ8),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -22386,7 +22317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:221" ht="409.6">
+    <row r="9" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9440156</v>
       </c>
@@ -22465,9 +22396,7 @@
       <c r="AH9" s="2">
         <v>0.5</v>
       </c>
-      <c r="AI9" s="37" t="s">
-        <v>1337</v>
-      </c>
+      <c r="AI9" s="37"/>
       <c r="AK9">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -22531,7 +22460,7 @@
         <v>1</v>
       </c>
       <c r="BH9" t="s">
-        <v>1296</v>
+        <v>1280</v>
       </c>
       <c r="BI9" cm="1">
         <f t="array" ref="BI9">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("path"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -22570,7 +22499,7 @@
         <v>1</v>
       </c>
       <c r="CG9" t="s">
-        <v>1296</v>
+        <v>1280</v>
       </c>
       <c r="CN9">
         <v>2019</v>
@@ -22592,7 +22521,7 @@
       <c r="DH9" s="33"/>
       <c r="DI9" s="33"/>
       <c r="FQ9" t="s">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="FR9" s="34" cm="1">
         <f t="array" ref="FR9">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ9),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -22741,7 +22670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:221" ht="409.6">
+    <row r="10" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7273631</v>
       </c>
@@ -22860,7 +22789,7 @@
         <v>6</v>
       </c>
       <c r="AY10" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
       <c r="AZ10" cm="1">
         <f t="array" ref="AZ10">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("prioritization"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("cost"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -22914,7 +22843,7 @@
         <v>1</v>
       </c>
       <c r="BX10" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
       <c r="BY10">
         <v>4</v>
@@ -22972,7 +22901,7 @@
       <c r="DI10" s="33"/>
       <c r="DT10" s="33"/>
       <c r="FQ10" t="s">
-        <v>1241</v>
+        <v>1225</v>
       </c>
       <c r="FR10" s="34" cm="1">
         <f t="array" ref="FR10">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ10),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -23121,7 +23050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:221" ht="409.6">
+    <row r="11" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8305939</v>
       </c>
@@ -23177,7 +23106,7 @@
         <v>169</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>1320</v>
+        <v>1304</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>91</v>
@@ -23236,7 +23165,7 @@
         <v>6</v>
       </c>
       <c r="AY11" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AZ11" cm="1">
         <f t="array" ref="AZ11">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("prioritization"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("other"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -23263,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="BH11" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
       <c r="BI11" cm="1">
         <f t="array" ref="BI11">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("firewall"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -23290,10 +23219,10 @@
         <v>0</v>
       </c>
       <c r="BX11" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="CG11" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
       <c r="CN11">
         <v>2021</v>
@@ -23314,7 +23243,7 @@
       <c r="DH11" s="33"/>
       <c r="DI11" s="33"/>
       <c r="FQ11" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="FR11" s="34" cm="1">
         <f t="array" ref="FR11">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ11),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -23463,7 +23392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:221" ht="409.6">
+    <row r="12" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9796413</v>
       </c>
@@ -23516,10 +23445,10 @@
         <v>58</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>1376</v>
+        <v>1358</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>1330</v>
+        <v>1314</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>130</v>
@@ -23578,7 +23507,7 @@
         <v>16</v>
       </c>
       <c r="BH12" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="BI12" cm="1">
         <f t="array" ref="BI12">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("cluster"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -23605,7 +23534,7 @@
         <v>0</v>
       </c>
       <c r="CG12" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="CN12">
         <v>2022</v>
@@ -23625,7 +23554,7 @@
       <c r="DH12" s="33"/>
       <c r="DI12" s="33"/>
       <c r="FQ12" t="s">
-        <v>1243</v>
+        <v>1227</v>
       </c>
       <c r="FR12" s="34" cm="1">
         <f t="array" ref="FR12">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ12),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -23774,7 +23703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:221" ht="409.6">
+    <row r="13" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>8452804</v>
       </c>
@@ -23828,10 +23757,10 @@
         <v>192</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>193</v>
@@ -23887,7 +23816,7 @@
         <v>7</v>
       </c>
       <c r="BH13" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
       <c r="BI13" cm="1">
         <f t="array" ref="BI13">SUMPRODUCT(($Y$2:$Y$996="PS")*(ISNUMBER(FIND(UPPER("selection"),UPPER($Z$2:$Z$996))))*(ISNUMBER(FIND(UPPER("design"),UPPER($AA$2:$AA$996))))*((ISNUMBER(FIND(UPPER("heuristic"),UPPER($AB$2:$AB$996))))*(NOT(ISNUMBER(FIND(UPPER("meta"),UPPER($AB$2:$AB$996)))))))</f>
@@ -23914,7 +23843,7 @@
         <v>0</v>
       </c>
       <c r="CG13" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
       <c r="CK13">
         <v>2</v>
@@ -23938,7 +23867,7 @@
       <c r="DH13" s="33"/>
       <c r="DI13" s="33"/>
       <c r="FQ13" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="FR13" s="34" cm="1">
         <f t="array" ref="FR13">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ13),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -24087,7 +24016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:221" ht="409.6">
+    <row r="14" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>7273420</v>
       </c>
@@ -24224,7 +24153,7 @@
       <c r="DH14" s="33"/>
       <c r="DI14" s="33"/>
       <c r="FQ14" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
       <c r="FR14" s="34" cm="1">
         <f t="array" ref="FR14">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ14),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -24373,7 +24302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:221" ht="409.6">
+    <row r="15" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>9787970</v>
       </c>
@@ -24506,7 +24435,7 @@
       <c r="DH15" s="33"/>
       <c r="DI15" s="33"/>
       <c r="FQ15" t="s">
-        <v>1246</v>
+        <v>1230</v>
       </c>
       <c r="FR15" s="34" cm="1">
         <f t="array" ref="FR15">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ15),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -24655,7 +24584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:221" ht="409.6">
+    <row r="16" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>8855691</v>
       </c>
@@ -24714,7 +24643,7 @@
         <v>90</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC16" s="2" t="s">
         <v>105</v>
@@ -24749,7 +24678,7 @@
         <v>1</v>
       </c>
       <c r="AP16" t="s">
-        <v>1227</v>
+        <v>1211</v>
       </c>
       <c r="AQ16">
         <v>3</v>
@@ -24764,7 +24693,7 @@
         <v>119</v>
       </c>
       <c r="CN16" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="CO16">
         <f>SUM(CO3:CO15)</f>
@@ -24788,14 +24717,14 @@
         <v>107</v>
       </c>
       <c r="FQ16" t="s">
-        <v>1247</v>
+        <v>1231</v>
       </c>
       <c r="FR16" s="34" cm="1">
         <f t="array" ref="FR16">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ16),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:221" ht="409.6">
+    <row r="17" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>8029584</v>
       </c>
@@ -24855,7 +24784,7 @@
         <v>169</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>1321</v>
+        <v>1305</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>91</v>
@@ -24894,14 +24823,14 @@
       </c>
       <c r="CZ17" s="33"/>
       <c r="FQ17" t="s">
-        <v>1248</v>
+        <v>1232</v>
       </c>
       <c r="FR17" s="34" cm="1">
         <f t="array" ref="FR17">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ17),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:221" ht="409.6">
+    <row r="18" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>7838169</v>
       </c>
@@ -24957,7 +24886,7 @@
         <v>256</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>1322</v>
+        <v>1306</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>206</v>
@@ -24998,14 +24927,14 @@
       </c>
       <c r="CZ18" s="33"/>
       <c r="FQ18" t="s">
-        <v>1249</v>
+        <v>1233</v>
       </c>
       <c r="FR18" s="34" cm="1">
         <f t="array" ref="FR18">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ18),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:221" ht="409.6">
+    <row r="19" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>6569743</v>
       </c>
@@ -25104,14 +25033,14 @@
       </c>
       <c r="CZ19" s="33"/>
       <c r="FQ19" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
       <c r="FR19" s="34" cm="1">
         <f t="array" ref="FR19">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ19),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
         <v>0</v>
       </c>
       <c r="GZ19" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="HA19" t="s">
         <v>46</v>
@@ -25126,34 +25055,34 @@
         <v>206</v>
       </c>
       <c r="HE19" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
       <c r="HF19" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
       <c r="HG19" t="s">
         <v>60</v>
       </c>
       <c r="HH19" t="s">
-        <v>1306</v>
+        <v>1290</v>
       </c>
       <c r="HI19" t="s">
-        <v>1307</v>
+        <v>1291</v>
       </c>
       <c r="HJ19" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="HK19" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="HL19" t="s">
-        <v>1313</v>
+        <v>1297</v>
       </c>
       <c r="HM19" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
     </row>
-    <row r="20" spans="1:221" ht="409.6">
+    <row r="20" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>8854718</v>
       </c>
@@ -25250,7 +25179,7 @@
       </c>
       <c r="CZ20" s="33"/>
       <c r="FQ20" t="s">
-        <v>1250</v>
+        <v>1234</v>
       </c>
       <c r="FR20" s="34" cm="1">
         <f t="array" ref="FR20">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ20),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -25312,7 +25241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:221" ht="409.6">
+    <row r="21" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>7272924</v>
       </c>
@@ -25368,7 +25297,7 @@
         <v>204</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>1323</v>
+        <v>1307</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>91</v>
@@ -25407,7 +25336,7 @@
       </c>
       <c r="CZ21" s="33"/>
       <c r="FQ21" t="s">
-        <v>1251</v>
+        <v>1235</v>
       </c>
       <c r="FR21" s="34" cm="1">
         <f t="array" ref="FR21">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ21),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -25469,7 +25398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:221" ht="409.6">
+    <row r="22" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>10196878</v>
       </c>
@@ -25566,7 +25495,7 @@
       </c>
       <c r="CZ22" s="33"/>
       <c r="FQ22" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
       <c r="FR22" s="34" cm="1">
         <f t="array" ref="FR22">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ22),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996))))</f>
@@ -25628,7 +25557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:221" ht="409.6">
+    <row r="23" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>7589817</v>
       </c>
@@ -25684,7 +25613,7 @@
         <v>256</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>1323</v>
+        <v>1307</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>91</v>
@@ -25724,7 +25653,7 @@
         <v>1</v>
       </c>
       <c r="FQ23" t="s">
-        <v>1269</v>
+        <v>1253</v>
       </c>
       <c r="FR23" s="34" cm="1">
         <f t="array" ref="FR23">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH("prioritization",LOWER(Z$2:Z$996)))*(NOT(ISNUMBER(SEARCH("coverage",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("requirement",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("probabilistic",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("distribution",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("clustering",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("history",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("model",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("cost-aware",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("similarity",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("input",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("structure",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("change",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("ml",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("heuristic",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("search",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("transfer",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("risk",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("nlp",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("design",LOWER(AA$2:AA$996))))))</f>
@@ -25786,7 +25715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:221" ht="409.6">
+    <row r="24" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>7381799</v>
       </c>
@@ -25880,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="FQ24" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
       <c r="GZ24">
         <v>2017</v>
@@ -25938,7 +25867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:221" ht="409.6">
+    <row r="25" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>10621714</v>
       </c>
@@ -26034,10 +25963,10 @@
         <v>1</v>
       </c>
       <c r="FQ25" t="s">
-        <v>1230</v>
+        <v>1214</v>
       </c>
       <c r="FR25" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="GZ25">
         <v>2018</v>
@@ -26095,7 +26024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:221" ht="409.6">
+    <row r="26" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>8530033</v>
       </c>
@@ -26156,7 +26085,7 @@
         <v>355</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>1349</v>
+        <v>1331</v>
       </c>
       <c r="AC26" s="2" t="s">
         <v>356</v>
@@ -26193,7 +26122,7 @@
         <v>1</v>
       </c>
       <c r="FQ26" t="s">
-        <v>1253</v>
+        <v>1237</v>
       </c>
       <c r="FR26" s="34" cm="1">
         <f t="array" ref="FR26">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ26),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -26255,7 +26184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:221" ht="409.6">
+    <row r="27" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>9825820</v>
       </c>
@@ -26353,7 +26282,7 @@
         <v>1</v>
       </c>
       <c r="FQ27" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="FR27" s="34" cm="1">
         <f t="array" ref="FR27">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ27),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -26415,7 +26344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:221" ht="409.6">
+    <row r="28" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>7272927</v>
       </c>
@@ -26507,7 +26436,7 @@
         <v>1</v>
       </c>
       <c r="FQ28" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="FR28" s="34" cm="1">
         <f t="array" ref="FR28">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ28),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -26569,7 +26498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:221" ht="409.6">
+    <row r="29" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>8539203</v>
       </c>
@@ -26625,10 +26554,10 @@
         <v>354</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>1324</v>
+        <v>1308</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>383</v>
@@ -26665,7 +26594,7 @@
         <v>1</v>
       </c>
       <c r="FQ29" t="s">
-        <v>1256</v>
+        <v>1240</v>
       </c>
       <c r="FR29" s="34" cm="1">
         <f t="array" ref="FR29">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ29),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -26727,7 +26656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:221" ht="409.6">
+    <row r="30" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>6928903</v>
       </c>
@@ -26821,7 +26750,7 @@
         <v>1</v>
       </c>
       <c r="FQ30" t="s">
-        <v>1257</v>
+        <v>1241</v>
       </c>
       <c r="FR30" s="34" cm="1">
         <f t="array" ref="FR30">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ30),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -26876,14 +26805,14 @@
       </c>
       <c r="HL30" cm="1">
         <f t="array" ref="HL30">SUMPRODUCT((Y$2:Y$996="PS")*(F$2:F$996=GZ30)*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*ISNUMBER(SEARCH(LOWER("greedy"),LOWER(AB$2:AB$996))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="HM30" cm="1">
         <f t="array" ref="HM30">SUMPRODUCT((Y$2:Y$996="PS")*(F$2:F$996=GZ30)*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*ISNUMBER(SEARCH(LOWER("dynamic"),LOWER(AB$2:AB$996))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:221" ht="409.6">
+    <row r="31" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>7091286</v>
       </c>
@@ -26983,7 +26912,7 @@
         <v>1</v>
       </c>
       <c r="FQ31" t="s">
-        <v>1258</v>
+        <v>1242</v>
       </c>
       <c r="FR31" s="34" cm="1">
         <f t="array" ref="FR31">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ31),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -27045,7 +26974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:221" ht="409.6">
+    <row r="32" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>10336260</v>
       </c>
@@ -27143,7 +27072,7 @@
         <v>1</v>
       </c>
       <c r="FQ32" t="s">
-        <v>1259</v>
+        <v>1243</v>
       </c>
       <c r="FR32" s="34" cm="1">
         <f t="array" ref="FR32">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ32),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -27205,7 +27134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:221" ht="409.6">
+    <row r="33" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>10304799</v>
       </c>
@@ -27258,7 +27187,7 @@
         <v>58</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA33" s="2"/>
       <c r="AB33" s="2"/>
@@ -27291,14 +27220,14 @@
         <v>0</v>
       </c>
       <c r="FQ33" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="FR33" s="34" cm="1">
         <f t="array" ref="FR33">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ33),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:221" ht="409.6">
+    <row r="34" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>10011478</v>
       </c>
@@ -27357,7 +27286,7 @@
         <v>407</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC34" s="2" t="s">
         <v>115</v>
@@ -27394,14 +27323,14 @@
         <v>1</v>
       </c>
       <c r="FQ34" t="s">
-        <v>1261</v>
+        <v>1245</v>
       </c>
       <c r="FR34" s="34" cm="1">
         <f t="array" ref="FR34">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ34),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:221" ht="144">
+    <row r="35" spans="1:221" ht="144" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
         <v>457</v>
       </c>
@@ -27462,17 +27391,17 @@
         <v>1</v>
       </c>
       <c r="FQ35" t="s">
-        <v>1262</v>
+        <v>1246</v>
       </c>
       <c r="FR35" s="34" cm="1">
         <f t="array" ref="FR35">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ35),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
         <v>0</v>
       </c>
       <c r="FV35" t="s">
-        <v>1273</v>
+        <v>1257</v>
       </c>
     </row>
-    <row r="36" spans="1:221" ht="409.6">
+    <row r="36" spans="1:221" ht="409.6" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
         <v>467</v>
       </c>
@@ -27495,10 +27424,10 @@
         <v>471</v>
       </c>
       <c r="AA36" s="7" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="AB36" s="7" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AC36" s="8"/>
       <c r="AD36" s="6" t="s">
@@ -27533,59 +27462,59 @@
         <v>0</v>
       </c>
       <c r="FQ36" t="s">
-        <v>1263</v>
+        <v>1247</v>
       </c>
       <c r="FR36" s="34" cm="1">
         <f t="array" ref="FR36">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ36),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
         <v>0</v>
       </c>
       <c r="FV36" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="FW36" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
       <c r="FX36" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="FY36" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
       <c r="FZ36" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="GA36" t="s">
         <v>863</v>
       </c>
       <c r="GB36" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
       <c r="GC36" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
       <c r="GD36" t="s">
-        <v>1296</v>
+        <v>1280</v>
       </c>
       <c r="GE36" t="s">
-        <v>1297</v>
+        <v>1281</v>
       </c>
       <c r="GF36" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
       <c r="GG36" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="GH36" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
       <c r="GI36" t="s">
-        <v>1300</v>
+        <v>1284</v>
       </c>
       <c r="GJ36" t="s">
-        <v>1301</v>
+        <v>1285</v>
       </c>
       <c r="GK36" t="s">
-        <v>1302</v>
+        <v>1286</v>
       </c>
       <c r="GL36" t="s">
         <v>407</v>
@@ -27597,61 +27526,61 @@
         <v>60</v>
       </c>
       <c r="GO36" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
       <c r="GP36" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
       <c r="GQ36" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
       <c r="GR36" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="GZ36" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="HA36" t="s">
-        <v>1275</v>
+        <v>1259</v>
       </c>
       <c r="HB36" t="s">
-        <v>1248</v>
+        <v>1232</v>
       </c>
       <c r="HC36" t="s">
-        <v>1247</v>
+        <v>1231</v>
       </c>
       <c r="HD36" t="s">
-        <v>1246</v>
+        <v>1230</v>
       </c>
       <c r="HE36" t="s">
-        <v>1276</v>
+        <v>1260</v>
       </c>
       <c r="HF36" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="HG36" t="s">
+        <v>1224</v>
+      </c>
+      <c r="HH36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="HI36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="HJ36" t="s">
+        <v>1263</v>
+      </c>
+      <c r="HK36" t="s">
+        <v>1241</v>
+      </c>
+      <c r="HL36" t="s">
+        <v>1264</v>
+      </c>
+      <c r="HM36" t="s">
         <v>1240</v>
       </c>
-      <c r="HH36" t="s">
-        <v>1277</v>
-      </c>
-      <c r="HI36" t="s">
-        <v>1278</v>
-      </c>
-      <c r="HJ36" t="s">
-        <v>1279</v>
-      </c>
-      <c r="HK36" t="s">
-        <v>1257</v>
-      </c>
-      <c r="HL36" t="s">
-        <v>1280</v>
-      </c>
-      <c r="HM36" t="s">
-        <v>1256</v>
-      </c>
     </row>
-    <row r="37" spans="1:221" ht="112">
+    <row r="37" spans="1:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
         <v>476</v>
       </c>
@@ -27714,7 +27643,7 @@
         <v>1</v>
       </c>
       <c r="FQ37" t="s">
-        <v>1251</v>
+        <v>1235</v>
       </c>
       <c r="FR37" s="34" cm="1">
         <f t="array" ref="FR37">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ37),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -27867,7 +27796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:221" ht="128">
+    <row r="38" spans="1:221" ht="128" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
         <v>485</v>
       </c>
@@ -27890,7 +27819,7 @@
         <v>489</v>
       </c>
       <c r="AA38" s="10" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
       <c r="AB38" s="10" t="s">
         <v>91</v>
@@ -27928,7 +27857,7 @@
         <v>0</v>
       </c>
       <c r="FQ38" t="s">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="FR38" s="34" cm="1">
         <f t="array" ref="FR38">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ38),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -28081,7 +28010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:221" ht="128">
+    <row r="39" spans="1:221" ht="128" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
         <v>494</v>
       </c>
@@ -28104,10 +28033,10 @@
         <v>498</v>
       </c>
       <c r="AA39" s="12" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="AB39" s="12" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AC39" s="12"/>
       <c r="AD39" s="12" t="s">
@@ -28142,7 +28071,7 @@
         <v>0</v>
       </c>
       <c r="FQ39" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
       <c r="FR39" s="34" cm="1">
         <f t="array" ref="FR39">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ39),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -28295,7 +28224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:221" ht="160">
+    <row r="40" spans="1:221" ht="160" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
         <v>503</v>
       </c>
@@ -28315,7 +28244,7 @@
         <v>58</v>
       </c>
       <c r="Z40" s="13" t="s">
-        <v>1377</v>
+        <v>1359</v>
       </c>
       <c r="AA40" s="14" t="s">
         <v>129</v>
@@ -28356,7 +28285,7 @@
         <v>0</v>
       </c>
       <c r="FQ40" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
       <c r="FR40" s="34" cm="1">
         <f t="array" ref="FR40">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ40),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -28509,7 +28438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:221" ht="144">
+    <row r="41" spans="1:221" ht="144" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
         <v>511</v>
       </c>
@@ -28570,7 +28499,7 @@
         <v>1</v>
       </c>
       <c r="FQ41" t="s">
-        <v>1234</v>
+        <v>1218</v>
       </c>
       <c r="FR41" s="34" cm="1">
         <f t="array" ref="FR41">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ41),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -28723,7 +28652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:221" ht="112">
+    <row r="42" spans="1:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
         <v>520</v>
       </c>
@@ -28749,7 +28678,7 @@
         <v>525</v>
       </c>
       <c r="AB42" s="7" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>383</v>
@@ -28786,7 +28715,7 @@
         <v>0</v>
       </c>
       <c r="FQ42" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
       <c r="FR42" s="34" cm="1">
         <f t="array" ref="FR42">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ42),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -28939,7 +28868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:221" ht="80">
+    <row r="43" spans="1:221" ht="80" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
         <v>530</v>
       </c>
@@ -28986,7 +28915,7 @@
         <v>0</v>
       </c>
       <c r="FQ43" t="s">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="FR43" s="34" cm="1">
         <f t="array" ref="FR43">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ43),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -29139,7 +29068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:221" ht="112">
+    <row r="44" spans="1:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
         <v>535</v>
       </c>
@@ -29162,7 +29091,7 @@
         <v>539</v>
       </c>
       <c r="AA44" s="7" t="s">
-        <v>1238</v>
+        <v>1222</v>
       </c>
       <c r="AB44" s="7" t="s">
         <v>91</v>
@@ -29200,7 +29129,7 @@
         <v>1</v>
       </c>
       <c r="FQ44" t="s">
-        <v>1239</v>
+        <v>1223</v>
       </c>
       <c r="FR44" s="34" cm="1">
         <f t="array" ref="FR44">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ44),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -29353,7 +29282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:221" ht="192">
+    <row r="45" spans="1:221" ht="192" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
         <v>544</v>
       </c>
@@ -29379,7 +29308,7 @@
         <v>407</v>
       </c>
       <c r="AB45" s="7" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC45" s="8"/>
       <c r="AD45" s="7" t="s">
@@ -29414,7 +29343,7 @@
         <v>1</v>
       </c>
       <c r="FQ45" t="s">
-        <v>1241</v>
+        <v>1225</v>
       </c>
       <c r="FR45" s="34" cm="1">
         <f t="array" ref="FR45">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ45),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -29567,7 +29496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:221" ht="80">
+    <row r="46" spans="1:221" ht="80" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
         <v>555</v>
       </c>
@@ -29614,7 +29543,7 @@
         <v>0</v>
       </c>
       <c r="FQ46" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="FR46" s="34" cm="1">
         <f t="array" ref="FR46">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH(LOWER(FQ46),LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996))))</f>
@@ -29767,7 +29696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:221" ht="80">
+    <row r="47" spans="1:221" ht="80" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
         <v>560</v>
       </c>
@@ -29814,7 +29743,7 @@
         <v>0</v>
       </c>
       <c r="FQ47" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
       <c r="FR47" s="34" cm="1">
         <f t="array" ref="FR47">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH("selection",LOWER(Z$2:Z$996)))*(NOT(ISNUMBER(SEARCH("integer",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("data-flow",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("symbolic",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("dynamic",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("graph",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("textual",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("sdg",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("path",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("mod",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("firewall",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("cluster",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("design",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("hybrid",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("selection",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("detection",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("coverage",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("change",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("model",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("history",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("cost-aware",LOWER(AA$2:AA$996)))))*(NOT(ISNUMBER(SEARCH("similarity",LOWER(AA$2:AA$996))))))</f>
@@ -29967,7 +29896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:221" ht="144">
+    <row r="48" spans="1:221" ht="144" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
         <v>564</v>
       </c>
@@ -29993,7 +29922,7 @@
         <v>407</v>
       </c>
       <c r="AB48" s="7" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC48" s="7"/>
       <c r="AD48" s="7" t="s">
@@ -30174,7 +30103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:221" ht="144">
+    <row r="49" spans="3:221" ht="144" x14ac:dyDescent="0.2">
       <c r="C49" t="s">
         <v>573</v>
       </c>
@@ -30200,7 +30129,7 @@
         <v>577</v>
       </c>
       <c r="AB49" s="7" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC49" s="7"/>
       <c r="AD49" s="6" t="s">
@@ -30381,7 +30310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:221" ht="96">
+    <row r="50" spans="3:221" ht="96" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
         <v>582</v>
       </c>
@@ -30404,10 +30333,10 @@
         <v>586</v>
       </c>
       <c r="AA50" s="18" t="s">
-        <v>1325</v>
+        <v>1309</v>
       </c>
       <c r="AB50" s="18" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AC50" s="18"/>
       <c r="AD50" s="18" t="s">
@@ -30448,10 +30377,10 @@
         <v>3</v>
       </c>
       <c r="FQ50" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
     </row>
-    <row r="51" spans="3:221" ht="96">
+    <row r="51" spans="3:221" ht="96" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
         <v>591</v>
       </c>
@@ -30512,13 +30441,13 @@
         <v>1</v>
       </c>
       <c r="FQ51" t="s">
-        <v>1230</v>
+        <v>1214</v>
       </c>
       <c r="FR51" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
     </row>
-    <row r="52" spans="3:221" ht="112">
+    <row r="52" spans="3:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C52" t="s">
         <v>599</v>
       </c>
@@ -30538,13 +30467,13 @@
         <v>58</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>1375</v>
+        <v>1357</v>
       </c>
       <c r="AA52" s="18" t="s">
         <v>407</v>
       </c>
       <c r="AB52" s="18" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC52" s="18" t="s">
         <v>383</v>
@@ -30581,14 +30510,14 @@
         <v>1</v>
       </c>
       <c r="FQ52" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
       <c r="FR52" s="34" cm="1">
         <f t="array" ref="FR52">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH("search-based",LOWER(AA$2:AA$996)))*ISNUMBER(SEARCH("minimization",LOWER(Z$2:Z$996))))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="3:221" ht="112">
+    <row r="53" spans="3:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
         <v>607</v>
       </c>
@@ -30649,14 +30578,14 @@
         <v>1</v>
       </c>
       <c r="FQ53" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
       <c r="FR53" s="34" cm="1">
         <f t="array" ref="FR53">SUMPRODUCT((Y$2:Y$996="PS")*ISNUMBER(SEARCH("minimization",LOWER(Z$2:Z$996)))*(NOT(ISNUMBER(SEARCH("search-based",LOWER(AA$2:AA$996))))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:221" ht="144">
+    <row r="54" spans="3:221" ht="144" x14ac:dyDescent="0.2">
       <c r="C54" t="s">
         <v>616</v>
       </c>
@@ -30682,7 +30611,7 @@
         <v>142</v>
       </c>
       <c r="AB54" s="18" t="s">
-        <v>1338</v>
+        <v>1321</v>
       </c>
       <c r="AC54" s="18"/>
       <c r="AD54" s="18" t="s">
@@ -30717,7 +30646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:221" ht="128">
+    <row r="55" spans="3:221" ht="128" x14ac:dyDescent="0.2">
       <c r="C55" t="s">
         <v>624</v>
       </c>
@@ -30778,7 +30707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:221" ht="160">
+    <row r="56" spans="3:221" ht="160" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
         <v>633</v>
       </c>
@@ -30801,10 +30730,10 @@
         <v>620</v>
       </c>
       <c r="AA56" s="18" t="s">
-        <v>1326</v>
+        <v>1310</v>
       </c>
       <c r="AB56" s="18" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC56" s="18" t="s">
         <v>383</v>
@@ -30841,7 +30770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:221" ht="112">
+    <row r="57" spans="3:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C57" t="s">
         <v>641</v>
       </c>
@@ -30858,7 +30787,7 @@
         <v>644</v>
       </c>
       <c r="M57" t="s">
-        <v>1372</v>
+        <v>1354</v>
       </c>
       <c r="Y57" t="s">
         <v>58</v>
@@ -30867,7 +30796,7 @@
         <v>620</v>
       </c>
       <c r="AA57" s="18" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="AB57" s="18" t="s">
         <v>130</v>
@@ -30905,7 +30834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:221">
+    <row r="58" spans="3:221" x14ac:dyDescent="0.2">
       <c r="C58" t="s">
         <v>649</v>
       </c>
@@ -30950,7 +30879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:221" ht="96">
+    <row r="59" spans="3:221" ht="96" x14ac:dyDescent="0.2">
       <c r="C59" t="s">
         <v>653</v>
       </c>
@@ -31013,7 +30942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:221" ht="80">
+    <row r="60" spans="3:221" ht="80" x14ac:dyDescent="0.2">
       <c r="C60" t="s">
         <v>661</v>
       </c>
@@ -31036,7 +30965,7 @@
         <v>515</v>
       </c>
       <c r="AA60" s="18" t="s">
-        <v>1238</v>
+        <v>1222</v>
       </c>
       <c r="AB60" s="18" t="s">
         <v>408</v>
@@ -31076,7 +31005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="3:221" ht="80">
+    <row r="61" spans="3:221" ht="80" x14ac:dyDescent="0.2">
       <c r="C61" t="s">
         <v>668</v>
       </c>
@@ -31102,7 +31031,7 @@
         <v>407</v>
       </c>
       <c r="AB61" s="21" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC61" s="21" t="s">
         <v>672</v>
@@ -31139,7 +31068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="3:221" ht="128">
+    <row r="62" spans="3:221" ht="128" x14ac:dyDescent="0.2">
       <c r="C62" t="s">
         <v>677</v>
       </c>
@@ -31162,10 +31091,10 @@
         <v>681</v>
       </c>
       <c r="AA62" s="18" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="AB62" s="18" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC62" s="18" t="s">
         <v>672</v>
@@ -31202,7 +31131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="3:221" ht="112">
+    <row r="63" spans="3:221" ht="112" x14ac:dyDescent="0.2">
       <c r="C63" t="s">
         <v>686</v>
       </c>
@@ -31228,7 +31157,7 @@
         <v>407</v>
       </c>
       <c r="AB63" s="21" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC63" s="21" t="s">
         <v>383</v>
@@ -31265,7 +31194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="3:221" ht="144">
+    <row r="64" spans="3:221" ht="144" x14ac:dyDescent="0.2">
       <c r="C64" s="2" t="s">
         <v>693</v>
       </c>
@@ -31291,7 +31220,7 @@
         <v>407</v>
       </c>
       <c r="AB64" s="23" t="s">
-        <v>1339</v>
+        <v>1322</v>
       </c>
       <c r="AC64" s="23" t="s">
         <v>115</v>
@@ -31328,7 +31257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:180" ht="187">
+    <row r="65" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A65" s="24">
         <v>9260075</v>
       </c>
@@ -31424,7 +31353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:180" ht="204">
+    <row r="66" spans="1:180" ht="204" x14ac:dyDescent="0.2">
       <c r="A66" s="24">
         <v>8914670</v>
       </c>
@@ -31485,7 +31414,7 @@
         <v>407</v>
       </c>
       <c r="AB66" s="26" t="s">
-        <v>1350</v>
+        <v>1332</v>
       </c>
       <c r="AC66" s="26" t="s">
         <v>725</v>
@@ -31524,7 +31453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:180" ht="221">
+    <row r="67" spans="1:180" ht="221" x14ac:dyDescent="0.2">
       <c r="A67" s="24">
         <v>8305938</v>
       </c>
@@ -31577,13 +31506,13 @@
         <v>58</v>
       </c>
       <c r="Z67" s="26" t="s">
-        <v>1374</v>
+        <v>1356</v>
       </c>
       <c r="AA67" s="26" t="s">
         <v>114</v>
       </c>
       <c r="AB67" s="26" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
       <c r="AC67" s="26"/>
       <c r="AD67" s="26" t="s">
@@ -31620,7 +31549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:180" ht="153">
+    <row r="68" spans="1:180" ht="153" x14ac:dyDescent="0.2">
       <c r="A68" s="24">
         <v>8453107</v>
       </c>
@@ -31675,7 +31604,7 @@
         <v>58</v>
       </c>
       <c r="Z68" s="26" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA68" s="26"/>
       <c r="AB68" s="26"/>
@@ -31706,7 +31635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:180" ht="187">
+    <row r="69" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A69" s="24">
         <v>8754416</v>
       </c>
@@ -31808,7 +31737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:180" ht="170">
+    <row r="70" spans="1:180" ht="170" x14ac:dyDescent="0.2">
       <c r="A70" s="24">
         <v>7582788</v>
       </c>
@@ -31859,10 +31788,10 @@
         <v>58</v>
       </c>
       <c r="Z70" s="26" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA70" s="26" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="AB70" s="26"/>
       <c r="AC70" s="26"/>
@@ -31892,10 +31821,10 @@
         <v>0</v>
       </c>
       <c r="FV70" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
     </row>
-    <row r="71" spans="1:180" ht="153">
+    <row r="71" spans="1:180" ht="153" x14ac:dyDescent="0.2">
       <c r="A71" s="24" t="s">
         <v>767</v>
       </c>
@@ -32003,16 +31932,16 @@
         <v>1</v>
       </c>
       <c r="FV71" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="FW71" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
       <c r="FX71" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
     </row>
-    <row r="72" spans="1:180" ht="119">
+    <row r="72" spans="1:180" ht="119" x14ac:dyDescent="0.2">
       <c r="A72" s="24" t="s">
         <v>785</v>
       </c>
@@ -32113,7 +32042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:180" ht="204">
+    <row r="73" spans="1:180" ht="204" x14ac:dyDescent="0.2">
       <c r="A73" s="24" t="s">
         <v>798</v>
       </c>
@@ -32176,7 +32105,7 @@
         <v>407</v>
       </c>
       <c r="AB73" s="26" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
       <c r="AC73" s="26" t="s">
         <v>808</v>
@@ -32226,7 +32155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:180" ht="187">
+    <row r="74" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A74" s="24" t="s">
         <v>813</v>
       </c>
@@ -32337,7 +32266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:180" ht="85">
+    <row r="75" spans="1:180" ht="85" x14ac:dyDescent="0.2">
       <c r="A75" s="24" t="s">
         <v>826</v>
       </c>
@@ -32402,7 +32331,7 @@
         <v>60</v>
       </c>
       <c r="AB75" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC75" s="26" t="s">
         <v>725</v>
@@ -32452,7 +32381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:180" ht="204">
+    <row r="76" spans="1:180" ht="204" x14ac:dyDescent="0.2">
       <c r="A76" s="24" t="s">
         <v>839</v>
       </c>
@@ -32515,7 +32444,7 @@
         <v>407</v>
       </c>
       <c r="AB76" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC76" s="26" t="s">
         <v>725</v>
@@ -32565,7 +32494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:180" ht="187">
+    <row r="77" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A77" s="24" t="s">
         <v>851</v>
       </c>
@@ -32625,10 +32554,10 @@
         <v>862</v>
       </c>
       <c r="AA77" s="26" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="AB77" s="26" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AC77" s="26" t="s">
         <v>725</v>
@@ -32678,7 +32607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:180" ht="153">
+    <row r="78" spans="1:180" ht="153" x14ac:dyDescent="0.2">
       <c r="A78" s="24" t="s">
         <v>867</v>
       </c>
@@ -32741,7 +32670,7 @@
         <v>407</v>
       </c>
       <c r="AB78" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC78" s="26" t="s">
         <v>725</v>
@@ -32791,7 +32720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:180" ht="255">
+    <row r="79" spans="1:180" ht="255" x14ac:dyDescent="0.2">
       <c r="A79" s="24" t="s">
         <v>879</v>
       </c>
@@ -32850,10 +32779,10 @@
         <v>58</v>
       </c>
       <c r="Z79" s="26" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA79" s="26" t="s">
-        <v>1355</v>
+        <v>1337</v>
       </c>
       <c r="AB79" s="26"/>
       <c r="AC79" s="26"/>
@@ -32894,7 +32823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:180" ht="187">
+    <row r="80" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A80" s="24" t="s">
         <v>890</v>
       </c>
@@ -32954,10 +32883,10 @@
         <v>899</v>
       </c>
       <c r="AA80" s="26" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="AB80" s="26" t="s">
-        <v>1340</v>
+        <v>1264</v>
       </c>
       <c r="AC80" s="26" t="s">
         <v>808</v>
@@ -33007,7 +32936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:180" ht="187">
+    <row r="81" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A81" s="24" t="s">
         <v>904</v>
       </c>
@@ -33070,7 +32999,7 @@
         <v>407</v>
       </c>
       <c r="AB81" s="26" t="s">
-        <v>1341</v>
+        <v>1323</v>
       </c>
       <c r="AC81" s="26" t="s">
         <v>725</v>
@@ -33120,7 +33049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:180" ht="170">
+    <row r="82" spans="1:180" ht="170" x14ac:dyDescent="0.2">
       <c r="A82" s="24"/>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
@@ -33201,7 +33130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:180" ht="187">
+    <row r="83" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A83" s="24"/>
       <c r="B83" s="25"/>
       <c r="C83" s="26" t="s">
@@ -33296,7 +33225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:180" ht="187">
+    <row r="84" spans="1:180" ht="187" x14ac:dyDescent="0.2">
       <c r="A84" s="24"/>
       <c r="B84" s="25"/>
       <c r="C84" s="26" t="s">
@@ -33341,7 +33270,7 @@
         <v>407</v>
       </c>
       <c r="AB84" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC84" s="26" t="s">
         <v>808</v>
@@ -33391,7 +33320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:180" ht="170">
+    <row r="85" spans="1:180" ht="170" x14ac:dyDescent="0.2">
       <c r="A85" s="24"/>
       <c r="B85" s="25"/>
       <c r="C85" s="26" t="s">
@@ -33436,7 +33365,7 @@
         <v>407</v>
       </c>
       <c r="AB85" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC85" s="26" t="s">
         <v>941</v>
@@ -33456,9 +33385,7 @@
       <c r="AH85" s="26">
         <v>1</v>
       </c>
-      <c r="AI85" s="26" t="s">
-        <v>944</v>
-      </c>
+      <c r="AI85" s="26"/>
       <c r="AJ85" s="25"/>
       <c r="AK85">
         <f t="shared" si="12"/>
@@ -33477,17 +33404,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:180" ht="102">
+    <row r="86" spans="1:180" ht="102" x14ac:dyDescent="0.2">
       <c r="A86" s="24"/>
       <c r="B86" s="25"/>
       <c r="C86" s="26" t="s">
+        <v>944</v>
+      </c>
+      <c r="D86" s="26" t="s">
         <v>945</v>
       </c>
-      <c r="D86" s="26" t="s">
+      <c r="E86" s="26" t="s">
         <v>946</v>
-      </c>
-      <c r="E86" s="26" t="s">
-        <v>947</v>
       </c>
       <c r="F86" s="25">
         <v>2016</v>
@@ -33496,7 +33423,7 @@
       <c r="H86" s="27"/>
       <c r="I86" s="27"/>
       <c r="J86" s="25" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="K86" s="25"/>
       <c r="L86" s="25"/>
@@ -33516,7 +33443,7 @@
         <v>44</v>
       </c>
       <c r="Z86" s="26" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AA86" s="39" t="s">
         <v>44</v>
@@ -33547,17 +33474,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:180" ht="153">
+    <row r="87" spans="1:180" ht="153" x14ac:dyDescent="0.2">
       <c r="A87" s="24"/>
       <c r="B87" s="25"/>
       <c r="C87" s="26" t="s">
+        <v>949</v>
+      </c>
+      <c r="D87" s="26" t="s">
         <v>950</v>
       </c>
-      <c r="D87" s="26" t="s">
+      <c r="E87" s="26" t="s">
         <v>951</v>
-      </c>
-      <c r="E87" s="26" t="s">
-        <v>952</v>
       </c>
       <c r="F87" s="25">
         <v>2018</v>
@@ -33566,7 +33493,7 @@
       <c r="H87" s="27"/>
       <c r="I87" s="27"/>
       <c r="J87" s="25" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="K87" s="25"/>
       <c r="L87" s="25"/>
@@ -33617,17 +33544,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:180" ht="136">
+    <row r="88" spans="1:180" ht="136" x14ac:dyDescent="0.2">
       <c r="A88" s="24"/>
       <c r="B88" s="25"/>
       <c r="C88" s="26" t="s">
+        <v>953</v>
+      </c>
+      <c r="D88" s="26" t="s">
         <v>954</v>
       </c>
-      <c r="D88" s="26" t="s">
+      <c r="E88" s="26" t="s">
         <v>955</v>
-      </c>
-      <c r="E88" s="26" t="s">
-        <v>956</v>
       </c>
       <c r="F88" s="25">
         <v>2019</v>
@@ -33636,7 +33563,7 @@
       <c r="H88" s="27"/>
       <c r="I88" s="27"/>
       <c r="J88" s="25" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="K88" s="25"/>
       <c r="L88" s="25"/>
@@ -33659,25 +33586,25 @@
         <v>724</v>
       </c>
       <c r="AA88" s="26" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AB88" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC88" s="26" t="s">
         <v>725</v>
       </c>
       <c r="AD88" s="26" t="s">
+        <v>958</v>
+      </c>
+      <c r="AE88" s="26" t="s">
         <v>959</v>
       </c>
-      <c r="AE88" s="26" t="s">
+      <c r="AF88" s="26" t="s">
         <v>960</v>
       </c>
-      <c r="AF88" s="26" t="s">
+      <c r="AG88" s="26" t="s">
         <v>961</v>
-      </c>
-      <c r="AG88" s="26" t="s">
-        <v>962</v>
       </c>
       <c r="AH88" s="26">
         <v>0.5</v>
@@ -33701,17 +33628,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:180" ht="409.6">
+    <row r="89" spans="1:180" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A89" s="24"/>
       <c r="B89" s="25"/>
       <c r="C89" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="D89" s="26" t="s">
         <v>963</v>
       </c>
-      <c r="D89" s="26" t="s">
+      <c r="E89" s="26" t="s">
         <v>964</v>
-      </c>
-      <c r="E89" s="26" t="s">
-        <v>965</v>
       </c>
       <c r="F89" s="25">
         <v>2019</v>
@@ -33720,7 +33647,7 @@
       <c r="H89" s="27"/>
       <c r="I89" s="27"/>
       <c r="J89" s="26" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K89" s="25"/>
       <c r="L89" s="25"/>
@@ -33740,28 +33667,28 @@
         <v>58</v>
       </c>
       <c r="Z89" s="26" t="s">
-        <v>1373</v>
+        <v>1355</v>
       </c>
       <c r="AA89" s="26" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="AB89" s="26" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AC89" s="26" t="s">
         <v>725</v>
       </c>
       <c r="AD89" s="26" t="s">
+        <v>967</v>
+      </c>
+      <c r="AE89" s="26" t="s">
         <v>968</v>
-      </c>
-      <c r="AE89" s="26" t="s">
-        <v>969</v>
       </c>
       <c r="AF89" s="26" t="s">
         <v>865</v>
       </c>
       <c r="AG89" s="26" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AH89" s="26">
         <v>0</v>
@@ -33785,17 +33712,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:180" ht="372">
+    <row r="90" spans="1:180" ht="372" x14ac:dyDescent="0.2">
       <c r="A90" s="24"/>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D90" s="26" t="s">
         <v>477</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F90" s="25">
         <v>2016</v>
@@ -33804,7 +33731,7 @@
       <c r="H90" s="27"/>
       <c r="I90" s="27"/>
       <c r="J90" s="25" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="K90" s="25"/>
       <c r="L90" s="25"/>
@@ -33824,28 +33751,28 @@
         <v>58</v>
       </c>
       <c r="Z90" s="26" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AA90" s="26" t="s">
         <v>407</v>
       </c>
       <c r="AB90" s="26" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="AC90" s="26" t="s">
         <v>725</v>
       </c>
       <c r="AD90" s="26" t="s">
+        <v>973</v>
+      </c>
+      <c r="AE90" s="26" t="s">
         <v>974</v>
       </c>
-      <c r="AE90" s="26" t="s">
+      <c r="AF90" s="26" t="s">
         <v>975</v>
       </c>
-      <c r="AF90" s="26" t="s">
+      <c r="AG90" s="26" t="s">
         <v>976</v>
-      </c>
-      <c r="AG90" s="26" t="s">
-        <v>977</v>
       </c>
       <c r="AH90" s="26">
         <v>0</v>
@@ -33869,17 +33796,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:180" ht="102">
+    <row r="91" spans="1:180" ht="102" x14ac:dyDescent="0.2">
       <c r="A91" s="24"/>
       <c r="B91" s="25"/>
       <c r="C91" s="26" t="s">
+        <v>977</v>
+      </c>
+      <c r="D91" s="26" t="s">
         <v>978</v>
       </c>
-      <c r="D91" s="26" t="s">
+      <c r="E91" s="26" t="s">
         <v>979</v>
-      </c>
-      <c r="E91" s="26" t="s">
-        <v>980</v>
       </c>
       <c r="F91" s="25">
         <v>2013</v>
@@ -33888,7 +33815,7 @@
       <c r="H91" s="27"/>
       <c r="I91" s="27"/>
       <c r="J91" s="25" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="K91" s="25"/>
       <c r="L91" s="25"/>
@@ -33908,10 +33835,10 @@
         <v>44</v>
       </c>
       <c r="Z91" s="26" t="s">
+        <v>981</v>
+      </c>
+      <c r="AA91" s="39" t="s">
         <v>982</v>
-      </c>
-      <c r="AA91" s="39" t="s">
-        <v>983</v>
       </c>
       <c r="AB91" s="39"/>
       <c r="AC91" s="39"/>
@@ -33939,17 +33866,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:180" ht="153">
+    <row r="92" spans="1:180" ht="153" x14ac:dyDescent="0.2">
       <c r="A92" s="24"/>
       <c r="B92" s="25"/>
       <c r="C92" s="26" t="s">
+        <v>983</v>
+      </c>
+      <c r="D92" s="26" t="s">
         <v>984</v>
       </c>
-      <c r="D92" s="26" t="s">
+      <c r="E92" s="26" t="s">
         <v>985</v>
-      </c>
-      <c r="E92" s="26" t="s">
-        <v>986</v>
       </c>
       <c r="F92" s="25">
         <v>2014</v>
@@ -33958,7 +33885,7 @@
       <c r="H92" s="27"/>
       <c r="I92" s="27"/>
       <c r="J92" s="25" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="K92" s="25"/>
       <c r="L92" s="25"/>
@@ -33978,28 +33905,28 @@
         <v>58</v>
       </c>
       <c r="Z92" s="26" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AA92" s="26" t="s">
         <v>129</v>
       </c>
       <c r="AB92" s="26" t="s">
-        <v>1351</v>
+        <v>1333</v>
       </c>
       <c r="AC92" s="26" t="s">
         <v>808</v>
       </c>
       <c r="AD92" s="26" t="s">
+        <v>988</v>
+      </c>
+      <c r="AE92" s="26" t="s">
         <v>989</v>
       </c>
-      <c r="AE92" s="26" t="s">
+      <c r="AF92" s="26" t="s">
         <v>990</v>
       </c>
-      <c r="AF92" s="26" t="s">
+      <c r="AG92" s="26" t="s">
         <v>991</v>
-      </c>
-      <c r="AG92" s="26" t="s">
-        <v>992</v>
       </c>
       <c r="AH92" s="26">
         <v>0</v>
@@ -34023,17 +33950,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:180" ht="119">
+    <row r="93" spans="1:180" ht="119" x14ac:dyDescent="0.2">
       <c r="A93" s="24"/>
       <c r="B93" s="25"/>
       <c r="C93" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="D93" s="26" t="s">
         <v>993</v>
       </c>
-      <c r="D93" s="26" t="s">
+      <c r="E93" s="26" t="s">
         <v>994</v>
-      </c>
-      <c r="E93" s="26" t="s">
-        <v>995</v>
       </c>
       <c r="F93" s="25">
         <v>2017</v>
@@ -34042,7 +33969,7 @@
       <c r="H93" s="27"/>
       <c r="I93" s="27"/>
       <c r="J93" s="25" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="K93" s="25"/>
       <c r="L93" s="25"/>
@@ -34062,7 +33989,7 @@
         <v>77</v>
       </c>
       <c r="Z93" s="26" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AA93" s="39" t="s">
         <v>77</v>
@@ -34093,19 +34020,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:180" ht="409.6">
+    <row r="94" spans="1:180" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>128</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>1000</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>1001</v>
       </c>
       <c r="F94" s="2">
         <v>2020</v>
@@ -34114,7 +34041,7 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
@@ -34134,25 +34061,25 @@
         <v>58</v>
       </c>
       <c r="Z94" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA94" s="2" t="s">
         <v>60</v>
       </c>
       <c r="AB94" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC94" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AD94" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="AD94" s="2" t="s">
+      <c r="AE94" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="AE94" s="2" t="s">
+      <c r="AF94" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="AF94" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="AG94" s="2" t="s">
         <v>66</v>
@@ -34178,19 +34105,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:180" ht="409.6">
+    <row r="95" spans="1:180" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>10</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>1008</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>1009</v>
       </c>
       <c r="F95" s="2">
         <v>2021</v>
@@ -34199,7 +34126,7 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
@@ -34219,7 +34146,7 @@
         <v>77</v>
       </c>
       <c r="Z95" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AA95" s="38"/>
       <c r="AB95" s="38"/>
@@ -34247,19 +34174,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:180" ht="409.6">
+    <row r="96" spans="1:180" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>130</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>1013</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>1014</v>
       </c>
       <c r="F96" s="2">
         <v>2013</v>
@@ -34268,7 +34195,7 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
@@ -34288,23 +34215,23 @@
         <v>58</v>
       </c>
       <c r="Z96" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA96" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AB96" s="2" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AE96" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="AE96" s="2" t="s">
+      <c r="AF96" s="2" t="s">
         <v>1017</v>
-      </c>
-      <c r="AF96" s="2" t="s">
-        <v>1018</v>
       </c>
       <c r="AG96" s="2" t="s">
         <v>66</v>
@@ -34330,19 +34257,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:40" ht="409.6">
+    <row r="97" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>131</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>1021</v>
       </c>
       <c r="F97" s="2">
         <v>2013</v>
@@ -34351,7 +34278,7 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
@@ -34371,28 +34298,28 @@
         <v>58</v>
       </c>
       <c r="Z97" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA97" s="2" t="s">
         <v>407</v>
       </c>
       <c r="AB97" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC97" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AD97" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AE97" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="AE97" s="2" t="s">
+      <c r="AF97" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="AF97" s="2" t="s">
+      <c r="AG97" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="AG97" s="2" t="s">
-        <v>1027</v>
       </c>
       <c r="AH97" s="2">
         <v>0</v>
@@ -34415,19 +34342,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:40" ht="409.6">
+    <row r="98" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>132</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="E98" s="2" t="s">
         <v>1029</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>1030</v>
       </c>
       <c r="F98" s="2">
         <v>2018</v>
@@ -34436,7 +34363,7 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
@@ -34456,23 +34383,23 @@
         <v>58</v>
       </c>
       <c r="Z98" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA98" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AB98" s="2" t="s">
         <v>206</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AE98" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AF98" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="AF98" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="AG98" s="2" t="s">
         <v>66</v>
@@ -34498,19 +34425,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:40" ht="409.6">
+    <row r="99" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>133</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>458</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F99" s="2">
         <v>2021</v>
@@ -34519,7 +34446,7 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
@@ -34539,33 +34466,31 @@
         <v>58</v>
       </c>
       <c r="Z99" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA99" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AB99" s="2" t="s">
         <v>1038</v>
-      </c>
-      <c r="AB99" s="2" t="s">
-        <v>1039</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AE99" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="AE99" s="2" t="s">
+      <c r="AF99" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="AF99" s="2" t="s">
+      <c r="AG99" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="AG99" s="2" t="s">
-        <v>1043</v>
-      </c>
       <c r="AH99" s="2">
         <v>1</v>
       </c>
-      <c r="AI99" s="2" t="s">
-        <v>1044</v>
-      </c>
+      <c r="AI99" s="2"/>
       <c r="AK99">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -34583,19 +34508,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:40" ht="409.6">
+    <row r="100" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>134</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>1045</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="F100" s="2">
         <v>2020</v>
@@ -34604,7 +34529,7 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
@@ -34624,23 +34549,23 @@
         <v>58</v>
       </c>
       <c r="Z100" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA100" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="AB100" s="2" t="s">
         <v>206</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AE100" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AF100" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="AE100" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="AF100" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="AG100" s="2" t="s">
         <v>66</v>
@@ -34648,9 +34573,7 @@
       <c r="AH100" s="2">
         <v>1</v>
       </c>
-      <c r="AI100" s="2" t="s">
-        <v>1053</v>
-      </c>
+      <c r="AI100" s="2"/>
       <c r="AK100">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -34668,19 +34591,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:40" ht="409.6">
+    <row r="101" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>135</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F101" s="2">
         <v>2022</v>
@@ -34689,7 +34612,7 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
@@ -34709,33 +34632,31 @@
         <v>58</v>
       </c>
       <c r="Z101" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA101" s="2" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="AB101" s="2" t="s">
         <v>206</v>
       </c>
       <c r="AC101" s="2"/>
       <c r="AD101" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AE101" s="2" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="AF101" s="2" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="AG101" s="2" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="AH101" s="2">
         <v>1</v>
       </c>
-      <c r="AI101" s="2" t="s">
-        <v>1053</v>
-      </c>
+      <c r="AI101" s="2"/>
       <c r="AK101">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -34753,19 +34674,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:40" ht="409.6">
+    <row r="102" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>136</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="F102" s="2">
         <v>2019</v>
@@ -34774,7 +34695,7 @@
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
@@ -34794,26 +34715,26 @@
         <v>58</v>
       </c>
       <c r="Z102" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA102" s="2" t="s">
         <v>407</v>
       </c>
       <c r="AB102" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC102" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="AD102" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AE102" s="2"/>
       <c r="AF102" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="AG102" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="AH102" s="2">
         <v>0</v>
@@ -34836,19 +34757,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:40" ht="409.6">
+    <row r="103" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>137</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F103" s="2">
         <v>2020</v>
@@ -34857,7 +34778,7 @@
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
@@ -34877,7 +34798,7 @@
         <v>58</v>
       </c>
       <c r="Z103" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA103" s="2" t="s">
         <v>407</v>
@@ -34887,13 +34808,13 @@
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AE103" s="2" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="AF103" s="2" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="AG103" s="2" t="s">
         <v>66</v>
@@ -34919,19 +34840,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:40" ht="409.6">
+    <row r="104" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>140</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="F104" s="2">
         <v>2018</v>
@@ -34940,7 +34861,7 @@
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
@@ -34960,33 +34881,31 @@
         <v>58</v>
       </c>
       <c r="Z104" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA104" s="2" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="AB104" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC104" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="AD104" s="2" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="AE104" s="2" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="AF104" s="2"/>
       <c r="AG104" s="2" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="AH104" s="2">
         <v>0.5</v>
       </c>
-      <c r="AI104" s="2" t="s">
-        <v>1082</v>
-      </c>
+      <c r="AI104" s="2"/>
       <c r="AK104">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35004,19 +34923,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:40" ht="409.6">
+    <row r="105" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>141</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="F105" s="2">
         <v>2021</v>
@@ -35025,7 +34944,7 @@
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
@@ -35045,7 +34964,7 @@
         <v>58</v>
       </c>
       <c r="Z105" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA105" s="2" t="s">
         <v>129</v>
@@ -35054,26 +34973,24 @@
         <v>206</v>
       </c>
       <c r="AC105" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="AD105" s="2" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="AE105" s="2" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="AF105" s="2" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="AG105" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="AH105" s="2">
         <v>1</v>
       </c>
-      <c r="AI105" s="2" t="s">
-        <v>1091</v>
-      </c>
+      <c r="AI105" s="2"/>
       <c r="AK105">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35091,19 +35008,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:40" ht="409.6">
+    <row r="106" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>142</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="F106" s="2">
         <v>2016</v>
@@ -35112,7 +35029,7 @@
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
@@ -35132,24 +35049,24 @@
         <v>58</v>
       </c>
       <c r="Z106" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA106" s="2" t="s">
-        <v>1333</v>
+        <v>1317</v>
       </c>
       <c r="AB106" s="2" t="s">
         <v>408</v>
       </c>
       <c r="AC106" s="2"/>
       <c r="AD106" s="2" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="AE106" s="2" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="AF106" s="2"/>
       <c r="AG106" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="AH106" s="2">
         <v>0</v>
@@ -35172,19 +35089,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:40" ht="409.6">
+    <row r="107" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>143</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="F107" s="2">
         <v>2017</v>
@@ -35193,7 +35110,7 @@
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
@@ -35213,26 +35130,26 @@
         <v>58</v>
       </c>
       <c r="Z107" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA107" s="2" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
       <c r="AB107" s="2" t="s">
         <v>408</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" s="2" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="AE107" s="2" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="AF107" s="2" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="AG107" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="AH107" s="2">
         <v>0</v>
@@ -35255,19 +35172,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:40" ht="409.6">
+    <row r="108" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>144</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="F108" s="2">
         <v>2018</v>
@@ -35276,7 +35193,7 @@
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
@@ -35296,35 +35213,33 @@
         <v>58</v>
       </c>
       <c r="Z108" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA108" s="2" t="s">
         <v>407</v>
       </c>
       <c r="AB108" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC108" s="2" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="AD108" s="2" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="AE108" s="2" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="AF108" s="2" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="AG108" s="2" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="AH108" s="2">
         <v>1</v>
       </c>
-      <c r="AI108" s="2" t="s">
-        <v>1114</v>
-      </c>
+      <c r="AI108" s="2"/>
       <c r="AK108">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35342,19 +35257,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:40" ht="409.6">
+    <row r="109" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>146</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="F109" s="2">
         <v>2017</v>
@@ -35363,7 +35278,7 @@
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
@@ -35383,10 +35298,10 @@
         <v>58</v>
       </c>
       <c r="Z109" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA109" s="2" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="AB109" s="2" t="s">
         <v>206</v>
@@ -35394,10 +35309,10 @@
       <c r="AC109" s="2"/>
       <c r="AD109" s="2"/>
       <c r="AE109" s="2" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="AF109" s="2" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="AG109" s="2" t="s">
         <v>714</v>
@@ -35423,19 +35338,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:40" ht="409.6">
+    <row r="110" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>147</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="F110" s="2">
         <v>2014</v>
@@ -35444,7 +35359,7 @@
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
@@ -35464,26 +35379,26 @@
         <v>58</v>
       </c>
       <c r="Z110" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA110" s="2" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="AB110" s="2" t="s">
         <v>91</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" s="2" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="AE110" s="2" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="AF110" s="2" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="AG110" s="2" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="AH110" s="2">
         <v>0</v>
@@ -35506,19 +35421,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:40" ht="409.6">
+    <row r="111" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>148</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="F111" s="2">
         <v>2014</v>
@@ -35527,7 +35442,7 @@
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
@@ -35547,33 +35462,31 @@
         <v>58</v>
       </c>
       <c r="Z111" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA111" s="2" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="AB111" s="2" t="s">
         <v>91</v>
       </c>
       <c r="AC111" s="2"/>
       <c r="AD111" s="2" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="AE111" s="2" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="AF111" s="2" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="AG111" s="2" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="AH111" s="2">
         <v>0.5</v>
       </c>
-      <c r="AI111" s="2" t="s">
-        <v>1139</v>
-      </c>
+      <c r="AI111" s="2"/>
       <c r="AK111">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35591,19 +35504,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:40" ht="409.6">
+    <row r="112" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>149</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="F112" s="2">
         <v>2018</v>
@@ -35612,7 +35525,7 @@
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
@@ -35632,21 +35545,21 @@
         <v>58</v>
       </c>
       <c r="Z112" s="2" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="AA112" s="2" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="AB112" s="2" t="s">
         <v>91</v>
       </c>
       <c r="AC112" s="2"/>
       <c r="AD112" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AE112" s="2"/>
       <c r="AF112" s="2" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="AG112" s="2" t="s">
         <v>66</v>
@@ -35654,9 +35567,7 @@
       <c r="AH112" s="2">
         <v>0</v>
       </c>
-      <c r="AI112" s="2" t="s">
-        <v>1146</v>
-      </c>
+      <c r="AI112" s="2"/>
       <c r="AK112">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35674,19 +35585,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:40" ht="409.6">
+    <row r="113" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>150</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="F113" s="2">
         <v>2023</v>
@@ -35695,7 +35606,7 @@
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
@@ -35715,23 +35626,23 @@
         <v>58</v>
       </c>
       <c r="Z113" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA113" s="2" t="s">
         <v>114</v>
       </c>
       <c r="AB113" s="2" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="AC113" s="2"/>
       <c r="AD113" s="2" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="AE113" s="2" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="AF113" s="2" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="AG113" s="2" t="s">
         <v>66</v>
@@ -35739,9 +35650,7 @@
       <c r="AH113" s="2">
         <v>1</v>
       </c>
-      <c r="AI113" s="2" t="s">
-        <v>1155</v>
-      </c>
+      <c r="AI113" s="2"/>
       <c r="AK113">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35759,19 +35668,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:40" ht="409.6">
+    <row r="114" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>151</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
-        <v>1156</v>
+        <v>1147</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1157</v>
+        <v>1148</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1158</v>
+        <v>1149</v>
       </c>
       <c r="F114" s="2">
         <v>2014</v>
@@ -35780,7 +35689,7 @@
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2" t="s">
-        <v>1159</v>
+        <v>1150</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
@@ -35800,23 +35709,23 @@
         <v>58</v>
       </c>
       <c r="Z114" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA114" s="2" t="s">
         <v>142</v>
       </c>
       <c r="AB114" s="2" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
       <c r="AC114" s="2"/>
       <c r="AD114" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AE114" s="2" t="s">
-        <v>1160</v>
+        <v>1151</v>
       </c>
       <c r="AF114" s="2" t="s">
-        <v>1161</v>
+        <v>1152</v>
       </c>
       <c r="AG114" s="2" t="s">
         <v>66</v>
@@ -35824,9 +35733,7 @@
       <c r="AH114" s="2">
         <v>0</v>
       </c>
-      <c r="AI114" s="2" t="s">
-        <v>1162</v>
-      </c>
+      <c r="AI114" s="2"/>
       <c r="AK114">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35844,19 +35751,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:40" ht="409.6">
+    <row r="115" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>152</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
       <c r="F115" s="2">
         <v>2015</v>
@@ -35865,7 +35772,7 @@
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
@@ -35885,7 +35792,7 @@
         <v>58</v>
       </c>
       <c r="Z115" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA115" s="2" t="s">
         <v>407</v>
@@ -35894,26 +35801,24 @@
         <v>206</v>
       </c>
       <c r="AC115" s="2" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="AD115" s="2" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
       <c r="AE115" s="2" t="s">
-        <v>1169</v>
+        <v>1159</v>
       </c>
       <c r="AF115" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="AG115" s="2" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
       <c r="AH115" s="2">
         <v>0.5</v>
       </c>
-      <c r="AI115" s="2" t="s">
-        <v>1171</v>
-      </c>
+      <c r="AI115" s="2"/>
       <c r="AK115">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -35931,19 +35836,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:40" ht="409.6">
+    <row r="116" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>154</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>1172</v>
+        <v>1161</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1173</v>
+        <v>1162</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1174</v>
+        <v>1163</v>
       </c>
       <c r="F116" s="2">
         <v>2021</v>
@@ -35952,7 +35857,7 @@
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2" t="s">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
@@ -35972,33 +35877,31 @@
         <v>58</v>
       </c>
       <c r="Z116" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA116" s="2" t="s">
         <v>114</v>
       </c>
       <c r="AB116" s="2" t="s">
-        <v>1176</v>
+        <v>1165</v>
       </c>
       <c r="AC116" s="2"/>
       <c r="AD116" s="2" t="s">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="AE116" s="2" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="AF116" s="2" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
       <c r="AG116" s="2" t="s">
-        <v>1180</v>
+        <v>1169</v>
       </c>
       <c r="AH116" s="2">
         <v>0</v>
       </c>
-      <c r="AI116" s="2" t="s">
-        <v>1181</v>
-      </c>
+      <c r="AI116" s="2"/>
       <c r="AK116">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -36016,19 +35919,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:40" ht="409.6">
+    <row r="117" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>155</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="F117" s="2">
         <v>2024</v>
@@ -36037,7 +35940,7 @@
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
@@ -36057,33 +35960,31 @@
         <v>58</v>
       </c>
       <c r="Z117" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA117" s="2" t="s">
         <v>114</v>
       </c>
       <c r="AB117" s="2" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" s="2" t="s">
-        <v>1187</v>
+        <v>1175</v>
       </c>
       <c r="AE117" s="2" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="AF117" s="2" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="AG117" s="2" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="AH117" s="2">
         <v>0</v>
       </c>
-      <c r="AI117" s="2" t="s">
-        <v>1191</v>
-      </c>
+      <c r="AI117" s="2"/>
       <c r="AK117">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -36101,19 +36002,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:40" ht="409.6">
+    <row r="118" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>156</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
       <c r="F118" s="2">
         <v>2022</v>
@@ -36122,7 +36023,7 @@
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2" t="s">
-        <v>1195</v>
+        <v>1182</v>
       </c>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
@@ -36142,33 +36043,31 @@
         <v>58</v>
       </c>
       <c r="Z118" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA118" s="2" t="s">
-        <v>1196</v>
+        <v>1183</v>
       </c>
       <c r="AB118" s="2" t="s">
         <v>408</v>
       </c>
       <c r="AC118" s="2"/>
       <c r="AD118" s="2" t="s">
-        <v>1197</v>
+        <v>1184</v>
       </c>
       <c r="AE118" s="2" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="AF118" s="2" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="AG118" s="2" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
       <c r="AH118" s="2">
         <v>0</v>
       </c>
-      <c r="AI118" s="2" t="s">
-        <v>1199</v>
-      </c>
+      <c r="AI118" s="2"/>
       <c r="AK118">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -36186,19 +36085,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:40" ht="409.6">
+    <row r="119" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>158</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>1200</v>
+        <v>1186</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1201</v>
+        <v>1187</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1202</v>
+        <v>1188</v>
       </c>
       <c r="F119" s="2">
         <v>2020</v>
@@ -36207,7 +36106,7 @@
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
       <c r="J119" s="2" t="s">
-        <v>1203</v>
+        <v>1189</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
@@ -36227,26 +36126,26 @@
         <v>58</v>
       </c>
       <c r="Z119" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AA119" s="2" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="AB119" s="2" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="AC119" s="2" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="AD119" s="2" t="s">
-        <v>1204</v>
+        <v>1190</v>
       </c>
       <c r="AE119" s="2" t="s">
-        <v>1205</v>
+        <v>1191</v>
       </c>
       <c r="AF119" s="2"/>
       <c r="AG119" s="2" t="s">
-        <v>1206</v>
+        <v>1192</v>
       </c>
       <c r="AH119" s="2">
         <v>1</v>
@@ -36269,19 +36168,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:40" ht="409.6">
+    <row r="120" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>159</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2" t="s">
-        <v>1207</v>
+        <v>1193</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>458</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="F120" s="2">
         <v>2015</v>
@@ -36290,7 +36189,7 @@
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2" t="s">
-        <v>1209</v>
+        <v>1195</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
@@ -36310,7 +36209,7 @@
         <v>58</v>
       </c>
       <c r="Z120" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA120" s="2" t="s">
         <v>60</v>
@@ -36319,16 +36218,16 @@
         <v>91</v>
       </c>
       <c r="AC120" s="2" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="AD120" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AE120" s="2" t="s">
-        <v>1210</v>
+        <v>1196</v>
       </c>
       <c r="AF120" s="2" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="AG120" s="2" t="s">
         <v>66</v>
@@ -36354,19 +36253,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:40" ht="409.6">
+    <row r="121" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>160</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="2" t="s">
-        <v>1211</v>
+        <v>1197</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>495</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>1212</v>
+        <v>1198</v>
       </c>
       <c r="F121" s="2">
         <v>2016</v>
@@ -36375,7 +36274,7 @@
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2" t="s">
-        <v>1213</v>
+        <v>1199</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
@@ -36395,20 +36294,20 @@
         <v>58</v>
       </c>
       <c r="Z121" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA121" s="2" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="AB121" s="2" t="s">
-        <v>1353</v>
+        <v>1335</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AE121" s="2" t="s">
-        <v>1214</v>
+        <v>1200</v>
       </c>
       <c r="AF121" s="2"/>
       <c r="AG121" s="2" t="s">
@@ -36417,9 +36316,7 @@
       <c r="AH121" s="2">
         <v>0.5</v>
       </c>
-      <c r="AI121" s="2" t="s">
-        <v>1215</v>
-      </c>
+      <c r="AI121" s="2"/>
       <c r="AK121">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -36437,19 +36334,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:40" ht="409.6">
+    <row r="122" spans="1:40" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>161</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>1216</v>
+        <v>1201</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>458</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1217</v>
+        <v>1202</v>
       </c>
       <c r="F122" s="2">
         <v>2022</v>
@@ -36458,7 +36355,7 @@
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2" t="s">
-        <v>1218</v>
+        <v>1203</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
@@ -36478,33 +36375,31 @@
         <v>58</v>
       </c>
       <c r="Z122" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AA122" s="2" t="s">
         <v>407</v>
       </c>
       <c r="AB122" s="2" t="s">
-        <v>1219</v>
+        <v>1204</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AE122" s="2" t="s">
-        <v>1220</v>
+        <v>1205</v>
       </c>
       <c r="AF122" s="2" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="AG122" s="2" t="s">
-        <v>1221</v>
+        <v>1206</v>
       </c>
       <c r="AH122" s="2">
         <v>1</v>
       </c>
-      <c r="AI122" s="2" t="s">
-        <v>1222</v>
-      </c>
+      <c r="AI122" s="2"/>
       <c r="AK122">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -36566,9 +36461,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B91C968-CFFD-1A41-862E-46C430B19788}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="31"/>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
